--- a/results_Uncertain_parameters_and_OF_values/simulacoes_por_cluster.xlsx
+++ b/results_Uncertain_parameters_and_OF_values/simulacoes_por_cluster.xlsx
@@ -527,13 +527,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sim265</t>
+          <t>Sim253</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -549,31 +549,31 @@
         <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6546396562573314</v>
+        <v>0.8800494602041387</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8802258103227316</v>
+        <v>0.9801349813900996</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6708486847082119</v>
+        <v>0.6362056904977501</v>
       </c>
       <c r="I3" t="n">
-        <v>20.05135300928963</v>
+        <v>20.21272297367112</v>
       </c>
       <c r="J3" t="n">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Sim253</t>
+          <t>Sim264</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -589,31 +589,31 @@
         <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8800494602041387</v>
+        <v>0.9681779203558112</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9801349813900996</v>
+        <v>0.8330447602765679</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6362056904977501</v>
+        <v>0.5733791854826861</v>
       </c>
       <c r="I4" t="n">
-        <v>20.21272297367112</v>
+        <v>20.21276763265253</v>
       </c>
       <c r="J4" t="n">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sim264</t>
+          <t>Sim255</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -629,31 +629,31 @@
         <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9681779203558112</v>
+        <v>0.6599710837636947</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8330447602765679</v>
+        <v>0.7551714868071477</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5733791854826861</v>
+        <v>0.6762957605664277</v>
       </c>
       <c r="I5" t="n">
-        <v>20.21276763265253</v>
+        <v>20.31885849820146</v>
       </c>
       <c r="J5" t="n">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Sim255</t>
+          <t>Sim194</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -669,31 +669,31 @@
         <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6599710837636947</v>
+        <v>0.9029180065302423</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7551714868071477</v>
+        <v>0.9255129250657248</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6762957605664277</v>
+        <v>0.6503097319377299</v>
       </c>
       <c r="I6" t="n">
-        <v>20.31885849820146</v>
+        <v>20.35078832456333</v>
       </c>
       <c r="J6" t="n">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Sim194</t>
+          <t>Sim188</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -709,31 +709,31 @@
         <v>0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9029180065302423</v>
+        <v>0.9445827585685068</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9255129250657248</v>
+        <v>0.7879679202645425</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6503097319377299</v>
+        <v>0.5045364713012247</v>
       </c>
       <c r="I7" t="n">
-        <v>20.35078832456333</v>
+        <v>20.39461720428645</v>
       </c>
       <c r="J7" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Sim256</t>
+          <t>Sim283</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -749,31 +749,31 @@
         <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.7032982502281092</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8784465181136041</v>
+        <v>0.9665412551469404</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7378118011167875</v>
+        <v>0.7639302349211632</v>
       </c>
       <c r="I8" t="n">
-        <v>20.37584345528036</v>
+        <v>20.39558779136541</v>
       </c>
       <c r="J8" t="n">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Sim188</t>
+          <t>Sim227</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -789,31 +789,31 @@
         <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9445827585685068</v>
+        <v>1.010092389221527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7879679202645425</v>
+        <v>0.9464681990564252</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5045364713012247</v>
+        <v>0.5574309039811548</v>
       </c>
       <c r="I9" t="n">
-        <v>20.39461720428645</v>
+        <v>20.39903549985454</v>
       </c>
       <c r="J9" t="n">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sim283</t>
+          <t>Sim228</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -826,34 +826,34 @@
         <v>0.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.5273754808969175</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7032982502281092</v>
+        <v>0.9952749058802068</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9665412551469404</v>
+        <v>0.8417652031616485</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7639302349211632</v>
+        <v>0.6268995853987001</v>
       </c>
       <c r="I10" t="n">
-        <v>20.39558779136541</v>
+        <v>20.42869187703781</v>
       </c>
       <c r="J10" t="n">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sim227</t>
+          <t>Sim243</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -869,31 +869,31 @@
         <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>1.010092389221527</v>
+        <v>0.7085848469649756</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9464681990564252</v>
+        <v>0.6815384149328454</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5574309039811548</v>
+        <v>0.6352224878759026</v>
       </c>
       <c r="I11" t="n">
-        <v>20.39903549985454</v>
+        <v>20.44238132527989</v>
       </c>
       <c r="J11" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Sim228</t>
+          <t>Sim263</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -906,34 +906,34 @@
         <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5273754808969175</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9952749058802068</v>
+        <v>1.029152573647481</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8417652031616485</v>
+        <v>0.9121300985733898</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6268995853987001</v>
+        <v>0.6023621486456163</v>
       </c>
       <c r="I12" t="n">
-        <v>20.42869187703781</v>
+        <v>20.44607831325841</v>
       </c>
       <c r="J12" t="n">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Sim243</t>
+          <t>Sim210</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -949,31 +949,31 @@
         <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7085848469649756</v>
+        <v>0.8982643916390752</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6815384149328454</v>
+        <v>0.7195188687998528</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6352224878759026</v>
+        <v>0.6340544176123536</v>
       </c>
       <c r="I13" t="n">
-        <v>20.44238132527989</v>
+        <v>20.50538581887489</v>
       </c>
       <c r="J13" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Sim263</t>
+          <t>Sim260</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -989,31 +989,31 @@
         <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1.029152573647481</v>
+        <v>0.6883265936698382</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9121300985733898</v>
+        <v>0.6824942241845192</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6023621486456163</v>
+        <v>0.6629388510316133</v>
       </c>
       <c r="I14" t="n">
-        <v>20.44607831325841</v>
+        <v>20.55285810201476</v>
       </c>
       <c r="J14" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Sim210</t>
+          <t>Sim229</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1029,31 +1029,31 @@
         <v>0.5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8982643916390752</v>
+        <v>0.9764387154508744</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7195188687998528</v>
+        <v>0.736466555203406</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6340544176123536</v>
+        <v>0.6026288324924983</v>
       </c>
       <c r="I15" t="n">
-        <v>20.50538581887489</v>
+        <v>20.58669348143913</v>
       </c>
       <c r="J15" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sim260</t>
+          <t>Sim298</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1069,31 +1069,31 @@
         <v>0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6883265936698382</v>
+        <v>1.030964463642867</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6824942241845192</v>
+        <v>0.9825684325545796</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6629388510316133</v>
+        <v>0.5917876301453074</v>
       </c>
       <c r="I16" t="n">
-        <v>20.55285810201476</v>
+        <v>20.59210808601908</v>
       </c>
       <c r="J16" t="n">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Sim229</t>
+          <t>Sim222</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1109,31 +1109,31 @@
         <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9764387154508744</v>
+        <v>0.6219846898308128</v>
       </c>
       <c r="G17" t="n">
-        <v>0.736466555203406</v>
+        <v>0.6960160208529139</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6026288324924983</v>
+        <v>0.6874973433960782</v>
       </c>
       <c r="I17" t="n">
-        <v>20.58669348143913</v>
+        <v>20.6347492496103</v>
       </c>
       <c r="J17" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Sim298</t>
+          <t>Sim201</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1149,31 +1149,31 @@
         <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>1.030964463642867</v>
+        <v>0.5799001529950845</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9825684325545796</v>
+        <v>0.7316540983716759</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5917876301453074</v>
+        <v>0.7332557146794358</v>
       </c>
       <c r="I18" t="n">
-        <v>20.59210808601908</v>
+        <v>20.63761729686441</v>
       </c>
       <c r="J18" t="n">
-        <v>298</v>
+        <v>201</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Sim222</t>
+          <t>Sim241</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1189,19 +1189,19 @@
         <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6219846898308128</v>
+        <v>0.5935465768473478</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6960160208529139</v>
+        <v>0.5474380492271285</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6874973433960782</v>
+        <v>0.5995898898557485</v>
       </c>
       <c r="I19" t="n">
-        <v>20.6347492496103</v>
+        <v>20.71961998481738</v>
       </c>
       <c r="J19" t="n">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1213,7 +1213,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Sim201</t>
+          <t>Sim192</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1229,31 +1229,31 @@
         <v>0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5799001529950845</v>
+        <v>1.19562369390614</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7316540983716759</v>
+        <v>0.8758106352283792</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7332557146794358</v>
+        <v>0.5093260479379814</v>
       </c>
       <c r="I20" t="n">
-        <v>20.63761729686441</v>
+        <v>20.76712749470226</v>
       </c>
       <c r="J20" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Sim241</t>
+          <t>Sim161</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1269,19 +1269,19 @@
         <v>0.5</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5935465768473478</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5474380492271285</v>
+        <v>0.7436778893195893</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5995898898557485</v>
+        <v>0.7509599565913773</v>
       </c>
       <c r="I21" t="n">
-        <v>20.71961998481738</v>
+        <v>20.78903503485302</v>
       </c>
       <c r="J21" t="n">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1293,7 +1293,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Sim192</t>
+          <t>Sim158</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1306,34 +1306,34 @@
         <v>0.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>0.6148546382980264</v>
       </c>
       <c r="F22" t="n">
-        <v>1.19562369390614</v>
+        <v>0.7210108900395958</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8758106352283792</v>
+        <v>0.834443993337176</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5093260479379814</v>
+        <v>0.7332350698650159</v>
       </c>
       <c r="I22" t="n">
-        <v>20.76712749470226</v>
+        <v>20.79356906554032</v>
       </c>
       <c r="J22" t="n">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Sim161</t>
+          <t>Sim193</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1346,28 +1346,28 @@
         <v>0.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>0.5984129934950575</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>0.9434224443822048</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7436778893195893</v>
+        <v>0.8151071541476985</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7509599565913773</v>
+        <v>0.6540371205408213</v>
       </c>
       <c r="I23" t="n">
-        <v>20.78903503485302</v>
+        <v>20.81724288797164</v>
       </c>
       <c r="J23" t="n">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1447,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1607,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1853,7 +1853,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Sim178</t>
+          <t>Sim230</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1866,34 +1866,34 @@
         <v>0.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5</v>
+        <v>0.7175512954570658</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6706780650702199</v>
+        <v>0.7671425562522712</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5985877799340157</v>
+        <v>0.7709505675603744</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8292013849887092</v>
+        <v>0.6509088037508256</v>
       </c>
       <c r="I36" t="n">
-        <v>21.03004932112616</v>
+        <v>21.00172427586616</v>
       </c>
       <c r="J36" t="n">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Sim175</t>
+          <t>Sim178</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1909,31 +1909,31 @@
         <v>0.5</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8936625988088979</v>
+        <v>0.6706780650702199</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8962017351056164</v>
+        <v>0.5985877799340157</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8533394618044282</v>
+        <v>0.8292013849887092</v>
       </c>
       <c r="I37" t="n">
-        <v>21.04183229656949</v>
+        <v>21.03004932112616</v>
       </c>
       <c r="J37" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Sim209</t>
+          <t>Sim175</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1949,31 +1949,31 @@
         <v>0.5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7823681143647534</v>
+        <v>0.8936625988088979</v>
       </c>
       <c r="G38" t="n">
-        <v>1.084945835949558</v>
+        <v>0.8962017351056164</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8608010830736597</v>
+        <v>0.8533394618044282</v>
       </c>
       <c r="I38" t="n">
-        <v>21.0536364767701</v>
+        <v>21.04183229656949</v>
       </c>
       <c r="J38" t="n">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Sim224</t>
+          <t>Sim209</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1989,31 +1989,31 @@
         <v>0.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7635011378515573</v>
+        <v>0.7823681143647534</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5</v>
+        <v>1.084945835949558</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8134073246353443</v>
+        <v>0.8608010830736597</v>
       </c>
       <c r="I39" t="n">
-        <v>21.06272489724295</v>
+        <v>21.0536364767701</v>
       </c>
       <c r="J39" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Sim176</t>
+          <t>Sim224</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2029,31 +2029,31 @@
         <v>0.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8118936044387417</v>
+        <v>0.7635011378515573</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5992395450852575</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7726266621914282</v>
+        <v>0.8134073246353443</v>
       </c>
       <c r="I40" t="n">
-        <v>21.09885083240359</v>
+        <v>21.06272489724295</v>
       </c>
       <c r="J40" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Sim213</t>
+          <t>Sim176</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2069,31 +2069,31 @@
         <v>0.5</v>
       </c>
       <c r="F41" t="n">
-        <v>0.691715681562008</v>
+        <v>0.8118936044387417</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6492369239223753</v>
+        <v>0.5992395450852575</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8664656676473038</v>
+        <v>0.7726266621914282</v>
       </c>
       <c r="I41" t="n">
-        <v>21.11898045623709</v>
+        <v>21.09885083240359</v>
       </c>
       <c r="J41" t="n">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Sim166</t>
+          <t>Sim213</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2109,31 +2109,31 @@
         <v>0.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8161216754677647</v>
+        <v>0.691715681562008</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5</v>
+        <v>0.6492369239223753</v>
       </c>
       <c r="H42" t="n">
-        <v>0.801985968879133</v>
+        <v>0.8664656676473038</v>
       </c>
       <c r="I42" t="n">
-        <v>21.12281907017736</v>
+        <v>21.11898045623709</v>
       </c>
       <c r="J42" t="n">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Sim204</t>
+          <t>Sim166</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2149,31 +2149,31 @@
         <v>0.5</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5</v>
+        <v>0.8161216754677647</v>
       </c>
       <c r="G43" t="n">
         <v>0.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8041007953333787</v>
+        <v>0.801985968879133</v>
       </c>
       <c r="I43" t="n">
-        <v>21.12495710876648</v>
+        <v>21.12281907017736</v>
       </c>
       <c r="J43" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Sim191</t>
+          <t>Sim204</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2189,31 +2189,31 @@
         <v>0.5</v>
       </c>
       <c r="F44" t="n">
-        <v>1.19121090854568</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6992134708504517</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7250530704427756</v>
+        <v>0.8041007953333787</v>
       </c>
       <c r="I44" t="n">
-        <v>21.12851133181332</v>
+        <v>21.12495710876648</v>
       </c>
       <c r="J44" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Sim208</t>
+          <t>Sim191</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2229,31 +2229,31 @@
         <v>0.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8661459700913986</v>
+        <v>1.19121090854568</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5866180033715725</v>
+        <v>0.6992134708504517</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7202433656090181</v>
+        <v>0.7250530704427756</v>
       </c>
       <c r="I45" t="n">
-        <v>21.13350794109571</v>
+        <v>21.12851133181332</v>
       </c>
       <c r="J45" t="n">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Sim169</t>
+          <t>Sim208</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2269,31 +2269,31 @@
         <v>0.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8595594882748152</v>
+        <v>0.8661459700913986</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5</v>
+        <v>0.5866180033715725</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7538535548930044</v>
+        <v>0.7202433656090181</v>
       </c>
       <c r="I46" t="n">
-        <v>21.17324220712602</v>
+        <v>21.13350794109571</v>
       </c>
       <c r="J46" t="n">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Sim250</t>
+          <t>Sim169</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2309,31 +2309,31 @@
         <v>0.5</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8450339272927757</v>
+        <v>0.8595594882748152</v>
       </c>
       <c r="G47" t="n">
-        <v>0.980386678060358</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>0.926463846242052</v>
+        <v>0.7538535548930044</v>
       </c>
       <c r="I47" t="n">
-        <v>21.18465788017363</v>
+        <v>21.17324220712602</v>
       </c>
       <c r="J47" t="n">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Sim155</t>
+          <t>Sim250</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2349,31 +2349,31 @@
         <v>0.5</v>
       </c>
       <c r="F48" t="n">
-        <v>1.35019972638122</v>
+        <v>0.8450339272927757</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9022885413974754</v>
+        <v>0.980386678060358</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8291184884023861</v>
+        <v>0.926463846242052</v>
       </c>
       <c r="I48" t="n">
-        <v>21.22265434547313</v>
+        <v>21.18465788017363</v>
       </c>
       <c r="J48" t="n">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Sim218</t>
+          <t>Sim155</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2389,31 +2389,31 @@
         <v>0.5</v>
       </c>
       <c r="F49" t="n">
-        <v>1.15335726591132</v>
+        <v>1.35019972638122</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7966386388557803</v>
+        <v>0.9022885413974754</v>
       </c>
       <c r="H49" t="n">
-        <v>0.855138811698124</v>
+        <v>0.8291184884023861</v>
       </c>
       <c r="I49" t="n">
-        <v>21.3105542844849</v>
+        <v>21.22265434547313</v>
       </c>
       <c r="J49" t="n">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Sim199</t>
+          <t>Sim219</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2426,34 +2426,34 @@
         <v>0.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5</v>
+        <v>0.6062286098624411</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5090613460410129</v>
+        <v>0.8488900333647152</v>
       </c>
       <c r="G50" t="n">
-        <v>0.83124686370041</v>
+        <v>0.5489767765843757</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9202780975591444</v>
+        <v>0.6070288076127434</v>
       </c>
       <c r="I50" t="n">
-        <v>21.31736890107326</v>
+        <v>21.23326336133828</v>
       </c>
       <c r="J50" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Sim349</t>
+          <t>Sim218</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2469,31 +2469,31 @@
         <v>0.5</v>
       </c>
       <c r="F51" t="n">
-        <v>0.667648025387277</v>
+        <v>1.15335726591132</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8982957483299181</v>
+        <v>0.7966386388557803</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5</v>
+        <v>0.855138811698124</v>
       </c>
       <c r="I51" t="n">
-        <v>19.79371942739746</v>
+        <v>21.3105542844849</v>
       </c>
       <c r="J51" t="n">
-        <v>349</v>
+        <v>218</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Sim354</t>
+          <t>Sim199</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2509,31 +2509,31 @@
         <v>0.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.673870696615274</v>
+        <v>0.5090613460410129</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9408238150382112</v>
+        <v>0.83124686370041</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5</v>
+        <v>0.9202780975591444</v>
       </c>
       <c r="I52" t="n">
-        <v>19.82673128793054</v>
+        <v>21.31736890107326</v>
       </c>
       <c r="J52" t="n">
-        <v>354</v>
+        <v>199</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Sim262</t>
+          <t>Sim156</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2546,34 +2546,34 @@
         <v>0.5</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5</v>
+        <v>0.6083697637447741</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7646244115100882</v>
+        <v>1.109414974234838</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9849800189172336</v>
+        <v>0.7606435662030911</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5769903660438551</v>
+        <v>0.7120782058261544</v>
       </c>
       <c r="I53" t="n">
-        <v>19.82874732395497</v>
+        <v>21.31861576498958</v>
       </c>
       <c r="J53" t="n">
-        <v>262</v>
+        <v>156</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Sim324</t>
+          <t>Sim349</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2589,19 +2589,19 @@
         <v>0.5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7303150120205026</v>
+        <v>0.667648025387277</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8912412684902027</v>
+        <v>0.8982957483299181</v>
       </c>
       <c r="H54" t="n">
         <v>0.5</v>
       </c>
       <c r="I54" t="n">
-        <v>19.82889012227807</v>
+        <v>19.79371942739746</v>
       </c>
       <c r="J54" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -2613,7 +2613,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Sim315</t>
+          <t>Sim354</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2629,19 +2629,19 @@
         <v>0.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.721924734739818</v>
+        <v>0.673870696615274</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8389116523677049</v>
+        <v>0.9408238150382112</v>
       </c>
       <c r="H55" t="n">
         <v>0.5</v>
       </c>
       <c r="I55" t="n">
-        <v>19.84616174922242</v>
+        <v>19.82673128793054</v>
       </c>
       <c r="J55" t="n">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="K55" t="n">
         <v>1</v>
@@ -2653,7 +2653,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Sim373</t>
+          <t>Sim262</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2669,19 +2669,19 @@
         <v>0.5</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7243753970552387</v>
+        <v>0.7646244115100882</v>
       </c>
       <c r="G56" t="n">
-        <v>1.003888155054957</v>
+        <v>0.9849800189172336</v>
       </c>
       <c r="H56" t="n">
-        <v>0.543700255400141</v>
+        <v>0.5769903660438551</v>
       </c>
       <c r="I56" t="n">
-        <v>19.86521696393386</v>
+        <v>19.82874732395497</v>
       </c>
       <c r="J56" t="n">
-        <v>373</v>
+        <v>262</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
@@ -2693,7 +2693,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Sim370</t>
+          <t>Sim324</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2709,19 +2709,19 @@
         <v>0.5</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7199346929606139</v>
+        <v>0.7303150120205026</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9815617267826016</v>
+        <v>0.8912412684902027</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5668396734763949</v>
+        <v>0.5</v>
       </c>
       <c r="I57" t="n">
-        <v>19.869125610581</v>
+        <v>19.82889012227807</v>
       </c>
       <c r="J57" t="n">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
@@ -2733,7 +2733,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Sim360</t>
+          <t>Sim315</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2749,19 +2749,19 @@
         <v>0.5</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7175149280238774</v>
+        <v>0.721924734739818</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9347484119094964</v>
+        <v>0.8389116523677049</v>
       </c>
       <c r="H58" t="n">
         <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>19.88271751453939</v>
+        <v>19.84616174922242</v>
       </c>
       <c r="J58" t="n">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="K58" t="n">
         <v>1</v>
@@ -2773,7 +2773,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Sim363</t>
+          <t>Sim373</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2789,19 +2789,19 @@
         <v>0.5</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7491408875418186</v>
+        <v>0.7243753970552387</v>
       </c>
       <c r="G59" t="n">
-        <v>1.024043938972604</v>
+        <v>1.003888155054957</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5601515288393788</v>
+        <v>0.543700255400141</v>
       </c>
       <c r="I59" t="n">
-        <v>19.88781791422335</v>
+        <v>19.86521696393386</v>
       </c>
       <c r="J59" t="n">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2813,7 +2813,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Sim374</t>
+          <t>Sim370</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2829,19 +2829,19 @@
         <v>0.5</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7535637895070992</v>
+        <v>0.7199346929606139</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8574120485426971</v>
+        <v>0.9815617267826016</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5</v>
+        <v>0.5668396734763949</v>
       </c>
       <c r="I60" t="n">
-        <v>19.89694815948714</v>
+        <v>19.869125610581</v>
       </c>
       <c r="J60" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -2853,7 +2853,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Sim325</t>
+          <t>Sim360</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2869,19 +2869,19 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6563596458197537</v>
+        <v>0.7175149280238774</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8033864051950853</v>
+        <v>0.9347484119094964</v>
       </c>
       <c r="H61" t="n">
         <v>0.5</v>
       </c>
       <c r="I61" t="n">
-        <v>19.9076251194195</v>
+        <v>19.88271751453939</v>
       </c>
       <c r="J61" t="n">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
@@ -2893,7 +2893,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Sim366</t>
+          <t>Sim363</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2909,19 +2909,19 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6782880766759938</v>
+        <v>0.7491408875418186</v>
       </c>
       <c r="G62" t="n">
-        <v>0.91499475765844</v>
+        <v>1.024043938972604</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5217605674135576</v>
+        <v>0.5601515288393788</v>
       </c>
       <c r="I62" t="n">
-        <v>19.91013495508172</v>
+        <v>19.88781791422335</v>
       </c>
       <c r="J62" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2933,7 +2933,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Sim266</t>
+          <t>Sim374</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2949,19 +2949,19 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6820571176089172</v>
+        <v>0.7535637895070992</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9890170858400033</v>
+        <v>0.8574120485426971</v>
       </c>
       <c r="H63" t="n">
         <v>0.5</v>
       </c>
       <c r="I63" t="n">
-        <v>19.91851978385319</v>
+        <v>19.89694815948714</v>
       </c>
       <c r="J63" t="n">
-        <v>266</v>
+        <v>374</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
@@ -2973,7 +2973,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Sim231</t>
+          <t>Sim325</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2989,19 +2989,19 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6251695448258154</v>
+        <v>0.6563596458197537</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8686156203301898</v>
+        <v>0.8033864051950853</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5325365580546998</v>
+        <v>0.5</v>
       </c>
       <c r="I64" t="n">
-        <v>19.92090157600369</v>
+        <v>19.9076251194195</v>
       </c>
       <c r="J64" t="n">
-        <v>231</v>
+        <v>325</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -3013,7 +3013,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Sim339</t>
+          <t>Sim366</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3029,19 +3029,19 @@
         <v>0.5</v>
       </c>
       <c r="F65" t="n">
-        <v>0.665032633703851</v>
+        <v>0.6782880766759938</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9803594252094234</v>
+        <v>0.91499475765844</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5</v>
+        <v>0.5217605674135576</v>
       </c>
       <c r="I65" t="n">
-        <v>19.92550799364484</v>
+        <v>19.91013495508172</v>
       </c>
       <c r="J65" t="n">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
@@ -3053,7 +3053,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Sim200</t>
+          <t>Sim266</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3069,19 +3069,19 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6838600770173657</v>
+        <v>0.6820571176089172</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9035013697267842</v>
+        <v>0.9890170858400033</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5949460705874342</v>
+        <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>19.92600199479501</v>
+        <v>19.91851978385319</v>
       </c>
       <c r="J66" t="n">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3093,7 +3093,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Sim378</t>
+          <t>Sim231</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3109,19 +3109,19 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7219939791692974</v>
+        <v>0.6251695448258154</v>
       </c>
       <c r="G67" t="n">
-        <v>0.966387721291985</v>
+        <v>0.8686156203301898</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5</v>
+        <v>0.5325365580546998</v>
       </c>
       <c r="I67" t="n">
-        <v>19.93164883850332</v>
+        <v>19.92090157600369</v>
       </c>
       <c r="J67" t="n">
-        <v>378</v>
+        <v>231</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -3133,7 +3133,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Sim371</t>
+          <t>Sim339</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3149,19 +3149,19 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7367495759175775</v>
+        <v>0.665032633703851</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9301179144049836</v>
+        <v>0.9803594252094234</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5124767915461463</v>
+        <v>0.5</v>
       </c>
       <c r="I68" t="n">
-        <v>19.93631351653192</v>
+        <v>19.92550799364484</v>
       </c>
       <c r="J68" t="n">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3173,7 +3173,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Sim293</t>
+          <t>Sim200</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3189,19 +3189,19 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5985444403685337</v>
+        <v>0.6838600770173657</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8648132580711027</v>
+        <v>0.9035013697267842</v>
       </c>
       <c r="H69" t="n">
-        <v>0.5568966888993022</v>
+        <v>0.5949460705874342</v>
       </c>
       <c r="I69" t="n">
-        <v>19.94364094768032</v>
+        <v>19.92600199479501</v>
       </c>
       <c r="J69" t="n">
-        <v>293</v>
+        <v>200</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
@@ -3213,7 +3213,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Sim252</t>
+          <t>Sim378</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3229,19 +3229,19 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.708813358739258</v>
+        <v>0.7219939791692974</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9710516279863416</v>
+        <v>0.966387721291985</v>
       </c>
       <c r="H70" t="n">
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>19.95489226927781</v>
+        <v>19.93164883850332</v>
       </c>
       <c r="J70" t="n">
-        <v>252</v>
+        <v>378</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
@@ -3253,7 +3253,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Sim368</t>
+          <t>Sim371</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3269,19 +3269,19 @@
         <v>0.5</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7814994943160665</v>
+        <v>0.7367495759175775</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9526490983616432</v>
+        <v>0.9301179144049836</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5323815148461118</v>
+        <v>0.5124767915461463</v>
       </c>
       <c r="I71" t="n">
-        <v>19.95904594923218</v>
+        <v>19.93631351653192</v>
       </c>
       <c r="J71" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -3293,7 +3293,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Sim278</t>
+          <t>Sim293</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3309,19 +3309,19 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6147775888197697</v>
+        <v>0.5985444403685337</v>
       </c>
       <c r="G72" t="n">
-        <v>0.832881852696273</v>
+        <v>0.8648132580711027</v>
       </c>
       <c r="H72" t="n">
-        <v>0.5424126250426831</v>
+        <v>0.5568966888993022</v>
       </c>
       <c r="I72" t="n">
-        <v>19.96845794525596</v>
+        <v>19.94364094768032</v>
       </c>
       <c r="J72" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
@@ -3333,7 +3333,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Sim350</t>
+          <t>Sim252</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3349,19 +3349,19 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7190285660739665</v>
+        <v>0.708813358739258</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9912051184532902</v>
+        <v>0.9710516279863416</v>
       </c>
       <c r="H73" t="n">
         <v>0.5</v>
       </c>
       <c r="I73" t="n">
-        <v>19.97173301958643</v>
+        <v>19.95489226927781</v>
       </c>
       <c r="J73" t="n">
-        <v>350</v>
+        <v>252</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
@@ -3373,7 +3373,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Sim384</t>
+          <t>Sim368</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3389,19 +3389,19 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7755140239363721</v>
+        <v>0.7814994943160665</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9351048305723044</v>
+        <v>0.9526490983616432</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5</v>
+        <v>0.5323815148461118</v>
       </c>
       <c r="I74" t="n">
-        <v>19.97705495454115</v>
+        <v>19.95904594923218</v>
       </c>
       <c r="J74" t="n">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
@@ -3413,7 +3413,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Sim328</t>
+          <t>Sim278</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3429,19 +3429,19 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7101430983649221</v>
+        <v>0.6147775888197697</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9835216340681781</v>
+        <v>0.832881852696273</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5650424180397943</v>
+        <v>0.5424126250426831</v>
       </c>
       <c r="I75" t="n">
-        <v>19.98380060046038</v>
+        <v>19.96845794525596</v>
       </c>
       <c r="J75" t="n">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
@@ -3453,7 +3453,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Sim326</t>
+          <t>Sim350</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3469,19 +3469,19 @@
         <v>0.5</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6590746073788497</v>
+        <v>0.7190285660739665</v>
       </c>
       <c r="G76" t="n">
-        <v>1.009067641352063</v>
+        <v>0.9912051184532902</v>
       </c>
       <c r="H76" t="n">
         <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>19.98598317034277</v>
+        <v>19.97173301958643</v>
       </c>
       <c r="J76" t="n">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -3493,7 +3493,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Sim340</t>
+          <t>Sim384</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3509,19 +3509,19 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="n">
-        <v>0.680764316287311</v>
+        <v>0.7755140239363721</v>
       </c>
       <c r="G77" t="n">
-        <v>0.992885295555522</v>
+        <v>0.9351048305723044</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5764895340527023</v>
+        <v>0.5</v>
       </c>
       <c r="I77" t="n">
-        <v>19.99286526328873</v>
+        <v>19.97705495454115</v>
       </c>
       <c r="J77" t="n">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
@@ -3533,7 +3533,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Sim341</t>
+          <t>Sim328</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3549,19 +3549,19 @@
         <v>0.5</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5406384256437935</v>
+        <v>0.7101430983649221</v>
       </c>
       <c r="G78" t="n">
-        <v>1.143314066904207</v>
+        <v>0.9835216340681781</v>
       </c>
       <c r="H78" t="n">
-        <v>0.5845837243999914</v>
+        <v>0.5650424180397943</v>
       </c>
       <c r="I78" t="n">
-        <v>19.99286526328873</v>
+        <v>19.98380060046038</v>
       </c>
       <c r="J78" t="n">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
@@ -3573,7 +3573,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Sim343</t>
+          <t>Sim326</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3589,19 +3589,19 @@
         <v>0.5</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6662629954037054</v>
+        <v>0.6590746073788497</v>
       </c>
       <c r="G79" t="n">
-        <v>1.034705926394679</v>
+        <v>1.009067641352063</v>
       </c>
       <c r="H79" t="n">
         <v>0.5</v>
       </c>
       <c r="I79" t="n">
-        <v>19.99426164442099</v>
+        <v>19.98598317034277</v>
       </c>
       <c r="J79" t="n">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
@@ -3613,7 +3613,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Sim310</t>
+          <t>Sim340</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3629,19 +3629,19 @@
         <v>0.5</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6106516302486218</v>
+        <v>0.680764316287311</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8339825270798847</v>
+        <v>0.992885295555522</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5</v>
+        <v>0.5764895340527023</v>
       </c>
       <c r="I80" t="n">
-        <v>20.00483932165938</v>
+        <v>19.99286526328873</v>
       </c>
       <c r="J80" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="K80" t="n">
         <v>1</v>
@@ -3653,7 +3653,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Sim345</t>
+          <t>Sim341</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3669,19 +3669,19 @@
         <v>0.5</v>
       </c>
       <c r="F81" t="n">
-        <v>0.76916880790664</v>
+        <v>0.5406384256437935</v>
       </c>
       <c r="G81" t="n">
-        <v>1.035776682974392</v>
+        <v>1.143314066904207</v>
       </c>
       <c r="H81" t="n">
-        <v>0.5179104820302269</v>
+        <v>0.5845837243999914</v>
       </c>
       <c r="I81" t="n">
-        <v>20.00489788428147</v>
+        <v>19.99286526328873</v>
       </c>
       <c r="J81" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K81" t="n">
         <v>1</v>
@@ -3693,7 +3693,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>Sim375</t>
+          <t>Sim343</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3709,19 +3709,19 @@
         <v>0.5</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7933825152053863</v>
+        <v>0.6662629954037054</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9929111417027492</v>
+        <v>1.034705926394679</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6128778054189931</v>
+        <v>0.5</v>
       </c>
       <c r="I82" t="n">
-        <v>20.02064880634487</v>
+        <v>19.99426164442099</v>
       </c>
       <c r="J82" t="n">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="K82" t="n">
         <v>1</v>
@@ -3733,7 +3733,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Sim377</t>
+          <t>Sim310</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3749,19 +3749,19 @@
         <v>0.5</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6085211814105269</v>
+        <v>0.6106516302486218</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8181294639670404</v>
+        <v>0.8339825270798847</v>
       </c>
       <c r="H83" t="n">
         <v>0.5</v>
       </c>
       <c r="I83" t="n">
-        <v>20.04451024485628</v>
+        <v>20.00483932165938</v>
       </c>
       <c r="J83" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
@@ -3773,7 +3773,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>Sim369</t>
+          <t>Sim345</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3789,19 +3789,19 @@
         <v>0.5</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7126629394093718</v>
+        <v>0.76916880790664</v>
       </c>
       <c r="G84" t="n">
-        <v>1.031925825940761</v>
+        <v>1.035776682974392</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5400386745744721</v>
+        <v>0.5179104820302269</v>
       </c>
       <c r="I84" t="n">
-        <v>20.04481649825361</v>
+        <v>20.00489788428147</v>
       </c>
       <c r="J84" t="n">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="K84" t="n">
         <v>1</v>
@@ -3813,7 +3813,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>Sim358</t>
+          <t>Sim375</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3829,19 +3829,19 @@
         <v>0.5</v>
       </c>
       <c r="F85" t="n">
-        <v>0.7538497683630726</v>
+        <v>0.7933825152053863</v>
       </c>
       <c r="G85" t="n">
-        <v>0.976506951308896</v>
+        <v>0.9929111417027492</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5</v>
+        <v>0.6128778054189931</v>
       </c>
       <c r="I85" t="n">
-        <v>20.05030559822359</v>
+        <v>20.02064880634487</v>
       </c>
       <c r="J85" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="K85" t="n">
         <v>1</v>
@@ -3853,7 +3853,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>Sim355</t>
+          <t>Sim377</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3869,19 +3869,19 @@
         <v>0.5</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6859340771623867</v>
+        <v>0.6085211814105269</v>
       </c>
       <c r="G86" t="n">
-        <v>1.064719141589692</v>
+        <v>0.8181294639670404</v>
       </c>
       <c r="H86" t="n">
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>20.05058733604717</v>
+        <v>20.04451024485628</v>
       </c>
       <c r="J86" t="n">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3893,7 +3893,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>Sim367</t>
+          <t>Sim369</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3909,19 +3909,19 @@
         <v>0.5</v>
       </c>
       <c r="F87" t="n">
-        <v>0.59104545324665</v>
+        <v>0.7126629394093718</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9922828534447556</v>
+        <v>1.031925825940761</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5530995123100196</v>
+        <v>0.5400386745744721</v>
       </c>
       <c r="I87" t="n">
-        <v>20.05365283721701</v>
+        <v>20.04481649825361</v>
       </c>
       <c r="J87" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K87" t="n">
         <v>1</v>
@@ -3933,7 +3933,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>Sim338</t>
+          <t>Sim358</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3949,19 +3949,19 @@
         <v>0.5</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6620339135613618</v>
+        <v>0.7538497683630726</v>
       </c>
       <c r="G88" t="n">
-        <v>1.022470693805177</v>
+        <v>0.976506951308896</v>
       </c>
       <c r="H88" t="n">
-        <v>0.5374263255449999</v>
+        <v>0.5</v>
       </c>
       <c r="I88" t="n">
-        <v>20.05702095667591</v>
+        <v>20.05030559822359</v>
       </c>
       <c r="J88" t="n">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -3973,7 +3973,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>Sim346</t>
+          <t>Sim355</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3989,19 +3989,19 @@
         <v>0.5</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6433093591616084</v>
+        <v>0.6859340771623867</v>
       </c>
       <c r="G89" t="n">
-        <v>1.007188014628971</v>
+        <v>1.064719141589692</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5897494905824064</v>
+        <v>0.5</v>
       </c>
       <c r="I89" t="n">
-        <v>20.05987495660164</v>
+        <v>20.05058733604717</v>
       </c>
       <c r="J89" t="n">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
@@ -4013,7 +4013,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>Sim311</t>
+          <t>Sim265</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4029,19 +4029,19 @@
         <v>0.5</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5775473601313168</v>
+        <v>0.6546396562573314</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8446030361644319</v>
+        <v>0.8802258103227316</v>
       </c>
       <c r="H90" t="n">
-        <v>0.6077676498460826</v>
+        <v>0.6708486847082119</v>
       </c>
       <c r="I90" t="n">
-        <v>20.0626589656376</v>
+        <v>20.05135300928963</v>
       </c>
       <c r="J90" t="n">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K90" t="n">
         <v>1</v>
@@ -4053,7 +4053,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>Sim198</t>
+          <t>Sim367</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4069,19 +4069,19 @@
         <v>0.5</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5924256270227966</v>
+        <v>0.59104545324665</v>
       </c>
       <c r="G91" t="n">
-        <v>0.8808373368329342</v>
+        <v>0.9922828534447556</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5</v>
+        <v>0.5530995123100196</v>
       </c>
       <c r="I91" t="n">
-        <v>20.06548217893893</v>
+        <v>20.05365283721701</v>
       </c>
       <c r="J91" t="n">
-        <v>198</v>
+        <v>367</v>
       </c>
       <c r="K91" t="n">
         <v>1</v>
@@ -4093,7 +4093,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>Sim359</t>
+          <t>Sim338</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4109,19 +4109,19 @@
         <v>0.5</v>
       </c>
       <c r="F92" t="n">
-        <v>0.694245581674469</v>
+        <v>0.6620339135613618</v>
       </c>
       <c r="G92" t="n">
-        <v>1.068555790592527</v>
+        <v>1.022470693805177</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5</v>
+        <v>0.5374263255449999</v>
       </c>
       <c r="I92" t="n">
-        <v>20.07141224189708</v>
+        <v>20.05702095667591</v>
       </c>
       <c r="J92" t="n">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4133,7 +4133,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>Sim352</t>
+          <t>Sim346</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4149,19 +4149,19 @@
         <v>0.5</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5877929025694938</v>
+        <v>0.6433093591616084</v>
       </c>
       <c r="G93" t="n">
-        <v>0.8278224781867461</v>
+        <v>1.007188014628971</v>
       </c>
       <c r="H93" t="n">
-        <v>0.5446055639820664</v>
+        <v>0.5897494905824064</v>
       </c>
       <c r="I93" t="n">
-        <v>20.07729473143525</v>
+        <v>20.05987495660164</v>
       </c>
       <c r="J93" t="n">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="K93" t="n">
         <v>1</v>
@@ -4173,7 +4173,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>Sim362</t>
+          <t>Sim311</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -4189,19 +4189,19 @@
         <v>0.5</v>
       </c>
       <c r="F94" t="n">
-        <v>0.687932407170455</v>
+        <v>0.5775473601313168</v>
       </c>
       <c r="G94" t="n">
-        <v>1.040115842827118</v>
+        <v>0.8446030361644319</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5891837949035175</v>
+        <v>0.6077676498460826</v>
       </c>
       <c r="I94" t="n">
-        <v>20.09046493229613</v>
+        <v>20.0626589656376</v>
       </c>
       <c r="J94" t="n">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
@@ -4213,7 +4213,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>Sim336</t>
+          <t>Sim198</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4229,19 +4229,19 @@
         <v>0.5</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7960915837172277</v>
+        <v>0.5924256270227966</v>
       </c>
       <c r="G95" t="n">
-        <v>1.048093429447801</v>
+        <v>0.8808373368329342</v>
       </c>
       <c r="H95" t="n">
-        <v>0.5111960632008262</v>
+        <v>0.5</v>
       </c>
       <c r="I95" t="n">
-        <v>20.10258997846939</v>
+        <v>20.06548217893893</v>
       </c>
       <c r="J95" t="n">
-        <v>336</v>
+        <v>198</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -4253,7 +4253,7 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>Sim381</t>
+          <t>Sim359</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -4269,19 +4269,19 @@
         <v>0.5</v>
       </c>
       <c r="F96" t="n">
-        <v>0.7015062102404743</v>
+        <v>0.694245581674469</v>
       </c>
       <c r="G96" t="n">
-        <v>1.052408276097768</v>
+        <v>1.068555790592527</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5411907001360624</v>
+        <v>0.5</v>
       </c>
       <c r="I96" t="n">
-        <v>20.10838575067829</v>
+        <v>20.07141224189708</v>
       </c>
       <c r="J96" t="n">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
@@ -4293,7 +4293,7 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Sim297</t>
+          <t>Sim352</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4309,19 +4309,19 @@
         <v>0.5</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5927968271120811</v>
+        <v>0.5877929025694938</v>
       </c>
       <c r="G97" t="n">
-        <v>1.011938292819799</v>
+        <v>0.8278224781867461</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5906819894877453</v>
+        <v>0.5446055639820664</v>
       </c>
       <c r="I97" t="n">
-        <v>20.11196362834811</v>
+        <v>20.07729473143525</v>
       </c>
       <c r="J97" t="n">
-        <v>297</v>
+        <v>352</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
@@ -4333,7 +4333,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>Sim300</t>
+          <t>Sim362</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -4349,19 +4349,19 @@
         <v>0.5</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5991396764451855</v>
+        <v>0.687932407170455</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9660589414723992</v>
+        <v>1.040115842827118</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6747732563173576</v>
+        <v>0.5891837949035175</v>
       </c>
       <c r="I98" t="n">
-        <v>20.13292705263245</v>
+        <v>20.09046493229613</v>
       </c>
       <c r="J98" t="n">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>Sim361</t>
+          <t>Sim336</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4389,19 +4389,19 @@
         <v>0.5</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7423709645097096</v>
+        <v>0.7960915837172277</v>
       </c>
       <c r="G99" t="n">
-        <v>1.041225460482291</v>
+        <v>1.048093429447801</v>
       </c>
       <c r="H99" t="n">
-        <v>0.5</v>
+        <v>0.5111960632008262</v>
       </c>
       <c r="I99" t="n">
-        <v>20.13573481498358</v>
+        <v>20.10258997846939</v>
       </c>
       <c r="J99" t="n">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
@@ -4413,7 +4413,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>Sim335</t>
+          <t>Sim381</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4429,19 +4429,19 @@
         <v>0.5</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6740756012930479</v>
+        <v>0.7015062102404743</v>
       </c>
       <c r="G100" t="n">
-        <v>1.013555317708734</v>
+        <v>1.052408276097768</v>
       </c>
       <c r="H100" t="n">
-        <v>0.6501960158199371</v>
+        <v>0.5411907001360624</v>
       </c>
       <c r="I100" t="n">
-        <v>20.1649140867062</v>
+        <v>20.10838575067829</v>
       </c>
       <c r="J100" t="n">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4453,7 +4453,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>Sim312</t>
+          <t>Sim297</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4469,19 +4469,19 @@
         <v>0.5</v>
       </c>
       <c r="F101" t="n">
-        <v>0.5891932810066239</v>
+        <v>0.5927968271120811</v>
       </c>
       <c r="G101" t="n">
-        <v>1.033226157900374</v>
+        <v>1.011938292819799</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6038797784802389</v>
+        <v>0.5906819894877453</v>
       </c>
       <c r="I101" t="n">
-        <v>20.1764704677048</v>
+        <v>20.11196362834811</v>
       </c>
       <c r="J101" t="n">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
@@ -4493,7 +4493,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>Sim301</t>
+          <t>Sim300</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4509,19 +4509,19 @@
         <v>0.5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7601675149009122</v>
+        <v>0.5991396764451855</v>
       </c>
       <c r="G102" t="n">
-        <v>1.072204870057863</v>
+        <v>0.9660589414723992</v>
       </c>
       <c r="H102" t="n">
-        <v>0.5</v>
+        <v>0.6747732563173576</v>
       </c>
       <c r="I102" t="n">
-        <v>20.18048537117533</v>
+        <v>20.13292705263245</v>
       </c>
       <c r="J102" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K102" t="n">
         <v>1</v>
@@ -4533,7 +4533,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>Sim383</t>
+          <t>Sim361</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4549,19 +4549,19 @@
         <v>0.5</v>
       </c>
       <c r="F103" t="n">
-        <v>0.579240733327008</v>
+        <v>0.7423709645097096</v>
       </c>
       <c r="G103" t="n">
-        <v>0.9959231102661552</v>
+        <v>1.041225460482291</v>
       </c>
       <c r="H103" t="n">
-        <v>0.5338244064571094</v>
+        <v>0.5</v>
       </c>
       <c r="I103" t="n">
-        <v>20.18307306355008</v>
+        <v>20.13573481498358</v>
       </c>
       <c r="J103" t="n">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4573,7 +4573,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>Sim233</t>
+          <t>Sim335</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4589,19 +4589,19 @@
         <v>0.5</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5423884379165773</v>
+        <v>0.6740756012930479</v>
       </c>
       <c r="G104" t="n">
-        <v>0.8541007619648554</v>
+        <v>1.013555317708734</v>
       </c>
       <c r="H104" t="n">
-        <v>0.5</v>
+        <v>0.6501960158199371</v>
       </c>
       <c r="I104" t="n">
-        <v>20.18730412575539</v>
+        <v>20.1649140867062</v>
       </c>
       <c r="J104" t="n">
-        <v>233</v>
+        <v>335</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -4613,7 +4613,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>Sim334</t>
+          <t>Sim312</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -4629,31 +4629,31 @@
         <v>0.5</v>
       </c>
       <c r="F105" t="n">
-        <v>0.8609244256435362</v>
+        <v>0.5891932810066239</v>
       </c>
       <c r="G105" t="n">
-        <v>1.066464184858885</v>
+        <v>1.033226157900374</v>
       </c>
       <c r="H105" t="n">
-        <v>0.5511139936278038</v>
+        <v>0.6038797784802389</v>
       </c>
       <c r="I105" t="n">
-        <v>20.19257153918689</v>
+        <v>20.1764704677048</v>
       </c>
       <c r="J105" t="n">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>Sim273</t>
+          <t>Sim301</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4669,19 +4669,19 @@
         <v>0.5</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6406070328289752</v>
+        <v>0.7601675149009122</v>
       </c>
       <c r="G106" t="n">
-        <v>1.085316244105633</v>
+        <v>1.072204870057863</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5066263916712352</v>
+        <v>0.5</v>
       </c>
       <c r="I106" t="n">
-        <v>20.19757184247256</v>
+        <v>20.18048537117533</v>
       </c>
       <c r="J106" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>Sim332</t>
+          <t>Sim383</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -4709,19 +4709,19 @@
         <v>0.5</v>
       </c>
       <c r="F107" t="n">
-        <v>0.5596501693848368</v>
+        <v>0.579240733327008</v>
       </c>
       <c r="G107" t="n">
-        <v>1.023449958088979</v>
+        <v>0.9959231102661552</v>
       </c>
       <c r="H107" t="n">
-        <v>0.5903977076548812</v>
+        <v>0.5338244064571094</v>
       </c>
       <c r="I107" t="n">
-        <v>20.20194698369207</v>
+        <v>20.18307306355008</v>
       </c>
       <c r="J107" t="n">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="K107" t="n">
         <v>1</v>
@@ -4733,7 +4733,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>Sim294</t>
+          <t>Sim233</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4749,19 +4749,19 @@
         <v>0.5</v>
       </c>
       <c r="F108" t="n">
-        <v>0.5</v>
+        <v>0.5423884379165773</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8873677362112296</v>
+        <v>0.8541007619648554</v>
       </c>
       <c r="H108" t="n">
-        <v>0.5644733126751911</v>
+        <v>0.5</v>
       </c>
       <c r="I108" t="n">
-        <v>20.20577285361534</v>
+        <v>20.18730412575539</v>
       </c>
       <c r="J108" t="n">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="K108" t="n">
         <v>1</v>
@@ -4773,7 +4773,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>Sim196</t>
+          <t>Sim334</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4789,31 +4789,31 @@
         <v>0.5</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5693489967885359</v>
+        <v>0.8609244256435362</v>
       </c>
       <c r="G109" t="n">
-        <v>0.7827706430974025</v>
+        <v>1.066464184858885</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6312606560758327</v>
+        <v>0.5511139936278038</v>
       </c>
       <c r="I109" t="n">
-        <v>20.21153592832975</v>
+        <v>20.19257153918689</v>
       </c>
       <c r="J109" t="n">
-        <v>196</v>
+        <v>334</v>
       </c>
       <c r="K109" t="n">
         <v>1</v>
       </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>Sim296</t>
+          <t>Sim273</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4829,19 +4829,19 @@
         <v>0.5</v>
       </c>
       <c r="F110" t="n">
-        <v>0.536563253634911</v>
+        <v>0.6406070328289752</v>
       </c>
       <c r="G110" t="n">
-        <v>0.9875226786970308</v>
+        <v>1.085316244105633</v>
       </c>
       <c r="H110" t="n">
-        <v>0.5899613961853957</v>
+        <v>0.5066263916712352</v>
       </c>
       <c r="I110" t="n">
-        <v>20.21881559133829</v>
+        <v>20.19757184247256</v>
       </c>
       <c r="J110" t="n">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="K110" t="n">
         <v>1</v>
@@ -4853,7 +4853,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>Sim212</t>
+          <t>Sim332</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4869,19 +4869,19 @@
         <v>0.5</v>
       </c>
       <c r="F111" t="n">
-        <v>0.5</v>
+        <v>0.5596501693848368</v>
       </c>
       <c r="G111" t="n">
-        <v>0.9247113992959908</v>
+        <v>1.023449958088979</v>
       </c>
       <c r="H111" t="n">
-        <v>0.6199361425606162</v>
+        <v>0.5903977076548812</v>
       </c>
       <c r="I111" t="n">
-        <v>20.22492194865476</v>
+        <v>20.20194698369207</v>
       </c>
       <c r="J111" t="n">
-        <v>212</v>
+        <v>332</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -4893,7 +4893,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>Sim323</t>
+          <t>Sim294</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4909,19 +4909,19 @@
         <v>0.5</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6401896498714894</v>
+        <v>0.5</v>
       </c>
       <c r="G112" t="n">
-        <v>1.088620803238627</v>
+        <v>0.8873677362112296</v>
       </c>
       <c r="H112" t="n">
-        <v>0.5</v>
+        <v>0.5644733126751911</v>
       </c>
       <c r="I112" t="n">
-        <v>20.2249467470742</v>
+        <v>20.20577285361534</v>
       </c>
       <c r="J112" t="n">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="K112" t="n">
         <v>1</v>
@@ -4933,7 +4933,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>Sim295</t>
+          <t>Sim196</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4949,19 +4949,19 @@
         <v>0.5</v>
       </c>
       <c r="F113" t="n">
-        <v>0.5148743306940131</v>
+        <v>0.5693489967885359</v>
       </c>
       <c r="G113" t="n">
-        <v>0.9559529228093556</v>
+        <v>0.7827706430974025</v>
       </c>
       <c r="H113" t="n">
-        <v>0.5501180164857513</v>
+        <v>0.6312606560758327</v>
       </c>
       <c r="I113" t="n">
-        <v>20.23203845125293</v>
+        <v>20.21153592832975</v>
       </c>
       <c r="J113" t="n">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="K113" t="n">
         <v>1</v>
@@ -4973,7 +4973,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>Sim303</t>
+          <t>Sim296</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4989,19 +4989,19 @@
         <v>0.5</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5747328971969233</v>
+        <v>0.536563253634911</v>
       </c>
       <c r="G114" t="n">
-        <v>0.9660037836155562</v>
+        <v>0.9875226786970308</v>
       </c>
       <c r="H114" t="n">
-        <v>0.5013750129866963</v>
+        <v>0.5899613961853957</v>
       </c>
       <c r="I114" t="n">
-        <v>20.24417962140012</v>
+        <v>20.21881559133829</v>
       </c>
       <c r="J114" t="n">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="K114" t="n">
         <v>1</v>
@@ -5013,7 +5013,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>Sim376</t>
+          <t>Sim212</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -5029,19 +5029,19 @@
         <v>0.5</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5696828345377732</v>
+        <v>0.5</v>
       </c>
       <c r="G115" t="n">
-        <v>1.058478513874148</v>
+        <v>0.9247113992959908</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5890439197007711</v>
+        <v>0.6199361425606162</v>
       </c>
       <c r="I115" t="n">
-        <v>20.24700039147576</v>
+        <v>20.22492194865476</v>
       </c>
       <c r="J115" t="n">
-        <v>376</v>
+        <v>212</v>
       </c>
       <c r="K115" t="n">
         <v>1</v>
@@ -5053,7 +5053,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>Sim268</t>
+          <t>Sim323</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -5069,19 +5069,19 @@
         <v>0.5</v>
       </c>
       <c r="F116" t="n">
-        <v>0.5320572767838352</v>
+        <v>0.6401896498714894</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8899279523046737</v>
+        <v>1.088620803238627</v>
       </c>
       <c r="H116" t="n">
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>20.25421558296301</v>
+        <v>20.2249467470742</v>
       </c>
       <c r="J116" t="n">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="K116" t="n">
         <v>1</v>
@@ -5093,7 +5093,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>Sim342</t>
+          <t>Sim295</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -5109,19 +5109,19 @@
         <v>0.5</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5599011705809959</v>
+        <v>0.5148743306940131</v>
       </c>
       <c r="G117" t="n">
-        <v>0.926974480458895</v>
+        <v>0.9559529228093556</v>
       </c>
       <c r="H117" t="n">
-        <v>0.5</v>
+        <v>0.5501180164857513</v>
       </c>
       <c r="I117" t="n">
-        <v>20.25615148094444</v>
+        <v>20.23203845125293</v>
       </c>
       <c r="J117" t="n">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="K117" t="n">
         <v>1</v>
@@ -5133,7 +5133,7 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>Sim238</t>
+          <t>Sim303</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -5149,19 +5149,19 @@
         <v>0.5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.7620221697812962</v>
+        <v>0.5747328971969233</v>
       </c>
       <c r="G118" t="n">
-        <v>1.050381213113086</v>
+        <v>0.9660037836155562</v>
       </c>
       <c r="H118" t="n">
-        <v>0.6374494044534245</v>
+        <v>0.5013750129866963</v>
       </c>
       <c r="I118" t="n">
-        <v>20.26834421225514</v>
+        <v>20.24417962140012</v>
       </c>
       <c r="J118" t="n">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="K118" t="n">
         <v>1</v>
@@ -5173,7 +5173,7 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Sim257</t>
+          <t>Sim376</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -5189,19 +5189,19 @@
         <v>0.5</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5</v>
+        <v>0.5696828345377732</v>
       </c>
       <c r="G119" t="n">
-        <v>0.9167732254049556</v>
+        <v>1.058478513874148</v>
       </c>
       <c r="H119" t="n">
-        <v>0.6422442037795779</v>
+        <v>0.5890439197007711</v>
       </c>
       <c r="I119" t="n">
-        <v>20.26844301520378</v>
+        <v>20.24700039147576</v>
       </c>
       <c r="J119" t="n">
-        <v>257</v>
+        <v>376</v>
       </c>
       <c r="K119" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>Sim327</t>
+          <t>Sim268</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -5229,19 +5229,19 @@
         <v>0.5</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6445454988250606</v>
+        <v>0.5320572767838352</v>
       </c>
       <c r="G120" t="n">
-        <v>1.087944570523712</v>
+        <v>0.8899279523046737</v>
       </c>
       <c r="H120" t="n">
-        <v>0.5621409480270603</v>
+        <v>0.5</v>
       </c>
       <c r="I120" t="n">
-        <v>20.27100852099552</v>
+        <v>20.25421558296301</v>
       </c>
       <c r="J120" t="n">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
@@ -5253,7 +5253,7 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Sim291</t>
+          <t>Sim342</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -5269,19 +5269,19 @@
         <v>0.5</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5413894058914741</v>
+        <v>0.5599011705809959</v>
       </c>
       <c r="G121" t="n">
-        <v>0.951967425257404</v>
+        <v>0.926974480458895</v>
       </c>
       <c r="H121" t="n">
         <v>0.5</v>
       </c>
       <c r="I121" t="n">
-        <v>20.27226856591937</v>
+        <v>20.25615148094444</v>
       </c>
       <c r="J121" t="n">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="K121" t="n">
         <v>1</v>
@@ -5293,7 +5293,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>Sim333</t>
+          <t>Sim238</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -5309,31 +5309,31 @@
         <v>0.5</v>
       </c>
       <c r="F122" t="n">
-        <v>0.9159386663111102</v>
+        <v>0.7620221697812962</v>
       </c>
       <c r="G122" t="n">
-        <v>1.005320344422706</v>
+        <v>1.050381213113086</v>
       </c>
       <c r="H122" t="n">
-        <v>0.5787530531628649</v>
+        <v>0.6374494044534245</v>
       </c>
       <c r="I122" t="n">
-        <v>20.28115755852102</v>
+        <v>20.26834421225514</v>
       </c>
       <c r="J122" t="n">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="K122" t="n">
         <v>1</v>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>Sim299</t>
+          <t>Sim257</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -5349,31 +5349,31 @@
         <v>0.5</v>
       </c>
       <c r="F123" t="n">
-        <v>0.9414337466331156</v>
+        <v>0.5</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9777577266050412</v>
+        <v>0.9167732254049556</v>
       </c>
       <c r="H123" t="n">
-        <v>0.5530708083328186</v>
+        <v>0.6422442037795779</v>
       </c>
       <c r="I123" t="n">
-        <v>20.28226308115142</v>
+        <v>20.26844301520378</v>
       </c>
       <c r="J123" t="n">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="K123" t="n">
         <v>1</v>
       </c>
       <c r="L123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>Sim305</t>
+          <t>Sim327</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -5389,19 +5389,19 @@
         <v>0.5</v>
       </c>
       <c r="F124" t="n">
-        <v>0.5179755853122521</v>
+        <v>0.6445454988250606</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9634348434101656</v>
+        <v>1.087944570523712</v>
       </c>
       <c r="H124" t="n">
-        <v>0.5267229580230547</v>
+        <v>0.5621409480270603</v>
       </c>
       <c r="I124" t="n">
-        <v>20.28846429173664</v>
+        <v>20.27100852099552</v>
       </c>
       <c r="J124" t="n">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="K124" t="n">
         <v>1</v>
@@ -5413,7 +5413,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>Sim235</t>
+          <t>Sim291</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -5429,19 +5429,19 @@
         <v>0.5</v>
       </c>
       <c r="F125" t="n">
-        <v>0.5</v>
+        <v>0.5413894058914741</v>
       </c>
       <c r="G125" t="n">
-        <v>0.8684331747625382</v>
+        <v>0.951967425257404</v>
       </c>
       <c r="H125" t="n">
-        <v>0.5128999632130758</v>
+        <v>0.5</v>
       </c>
       <c r="I125" t="n">
-        <v>20.29153554463327</v>
+        <v>20.27226856591937</v>
       </c>
       <c r="J125" t="n">
-        <v>235</v>
+        <v>291</v>
       </c>
       <c r="K125" t="n">
         <v>1</v>
@@ -5453,7 +5453,7 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>Sim331</t>
+          <t>Sim333</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -5469,31 +5469,31 @@
         <v>0.5</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5072876623942376</v>
+        <v>0.9159386663111102</v>
       </c>
       <c r="G126" t="n">
-        <v>1.008544406572994</v>
+        <v>1.005320344422706</v>
       </c>
       <c r="H126" t="n">
-        <v>0.5521586187085774</v>
+        <v>0.5787530531628649</v>
       </c>
       <c r="I126" t="n">
-        <v>20.29706207781267</v>
+        <v>20.28115755852102</v>
       </c>
       <c r="J126" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K126" t="n">
         <v>1</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>Sim314</t>
+          <t>Sim299</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -5509,31 +5509,31 @@
         <v>0.5</v>
       </c>
       <c r="F127" t="n">
-        <v>0.5135537417457124</v>
+        <v>0.9414337466331156</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8457113451265093</v>
+        <v>0.9777577266050412</v>
       </c>
       <c r="H127" t="n">
-        <v>0.5</v>
+        <v>0.5530708083328186</v>
       </c>
       <c r="I127" t="n">
-        <v>20.29770951782074</v>
+        <v>20.28226308115142</v>
       </c>
       <c r="J127" t="n">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="K127" t="n">
         <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>Sim246</t>
+          <t>Sim305</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -5549,19 +5549,19 @@
         <v>0.5</v>
       </c>
       <c r="F128" t="n">
-        <v>0.5</v>
+        <v>0.5179755853122521</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9363267033015528</v>
+        <v>0.9634348434101656</v>
       </c>
       <c r="H128" t="n">
-        <v>0.7078149671110128</v>
+        <v>0.5267229580230547</v>
       </c>
       <c r="I128" t="n">
-        <v>20.30637070094401</v>
+        <v>20.28846429173664</v>
       </c>
       <c r="J128" t="n">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="K128" t="n">
         <v>1</v>
@@ -5573,7 +5573,7 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>Sim279</t>
+          <t>Sim235</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -5592,16 +5592,16 @@
         <v>0.5</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8874514451476997</v>
+        <v>0.8684331747625382</v>
       </c>
       <c r="H129" t="n">
-        <v>0.5</v>
+        <v>0.5128999632130758</v>
       </c>
       <c r="I129" t="n">
-        <v>20.3083823881587</v>
+        <v>20.29153554463327</v>
       </c>
       <c r="J129" t="n">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="K129" t="n">
         <v>1</v>
@@ -5613,7 +5613,7 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>Sim380</t>
+          <t>Sim331</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -5629,19 +5629,19 @@
         <v>0.5</v>
       </c>
       <c r="F130" t="n">
-        <v>0.7551385869290712</v>
+        <v>0.5072876623942376</v>
       </c>
       <c r="G130" t="n">
-        <v>1.106991243572539</v>
+        <v>1.008544406572994</v>
       </c>
       <c r="H130" t="n">
-        <v>0.513336051869097</v>
+        <v>0.5521586187085774</v>
       </c>
       <c r="I130" t="n">
-        <v>20.31083048910995</v>
+        <v>20.29706207781267</v>
       </c>
       <c r="J130" t="n">
-        <v>380</v>
+        <v>331</v>
       </c>
       <c r="K130" t="n">
         <v>1</v>
@@ -5653,7 +5653,7 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>Sim236</t>
+          <t>Sim314</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -5669,19 +5669,19 @@
         <v>0.5</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5</v>
+        <v>0.5135537417457124</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9504735674517024</v>
+        <v>0.8457113451265093</v>
       </c>
       <c r="H131" t="n">
-        <v>0.6146940018590832</v>
+        <v>0.5</v>
       </c>
       <c r="I131" t="n">
-        <v>20.31137511016912</v>
+        <v>20.29770951782074</v>
       </c>
       <c r="J131" t="n">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="K131" t="n">
         <v>1</v>
@@ -5693,7 +5693,7 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>Sim288</t>
+          <t>Sim246</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -5709,19 +5709,19 @@
         <v>0.5</v>
       </c>
       <c r="F132" t="n">
-        <v>0.6378322417003632</v>
+        <v>0.5</v>
       </c>
       <c r="G132" t="n">
-        <v>1.110673194632721</v>
+        <v>0.9363267033015528</v>
       </c>
       <c r="H132" t="n">
-        <v>0.5</v>
+        <v>0.7078149671110128</v>
       </c>
       <c r="I132" t="n">
-        <v>20.32149686907976</v>
+        <v>20.30637070094401</v>
       </c>
       <c r="J132" t="n">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="K132" t="n">
         <v>1</v>
@@ -5733,7 +5733,7 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>Sim356</t>
+          <t>Sim279</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -5749,19 +5749,19 @@
         <v>0.5</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5294250520646335</v>
+        <v>0.5</v>
       </c>
       <c r="G133" t="n">
-        <v>0.9426532296751616</v>
+        <v>0.8874514451476997</v>
       </c>
       <c r="H133" t="n">
         <v>0.5</v>
       </c>
       <c r="I133" t="n">
-        <v>20.32274622971358</v>
+        <v>20.3083823881587</v>
       </c>
       <c r="J133" t="n">
-        <v>356</v>
+        <v>279</v>
       </c>
       <c r="K133" t="n">
         <v>1</v>
@@ -5773,7 +5773,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>Sim245</t>
+          <t>Sim380</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5789,19 +5789,19 @@
         <v>0.5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7933642490447225</v>
+        <v>0.7551385869290712</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6655950221897429</v>
+        <v>1.106991243572539</v>
       </c>
       <c r="H134" t="n">
-        <v>0.5</v>
+        <v>0.513336051869097</v>
       </c>
       <c r="I134" t="n">
-        <v>20.35196358649909</v>
+        <v>20.31083048910995</v>
       </c>
       <c r="J134" t="n">
-        <v>245</v>
+        <v>380</v>
       </c>
       <c r="K134" t="n">
         <v>1</v>
@@ -5813,7 +5813,7 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>Sim285</t>
+          <t>Sim236</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5829,19 +5829,19 @@
         <v>0.5</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7933996952180886</v>
+        <v>0.5</v>
       </c>
       <c r="G135" t="n">
-        <v>1.088849658652794</v>
+        <v>0.9504735674517024</v>
       </c>
       <c r="H135" t="n">
-        <v>0.6351747750136939</v>
+        <v>0.6146940018590832</v>
       </c>
       <c r="I135" t="n">
-        <v>20.35727000704251</v>
+        <v>20.31137511016912</v>
       </c>
       <c r="J135" t="n">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="K135" t="n">
         <v>1</v>
@@ -5853,7 +5853,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>Sim313</t>
+          <t>Sim288</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5869,19 +5869,19 @@
         <v>0.5</v>
       </c>
       <c r="F136" t="n">
-        <v>0.5537108322845353</v>
+        <v>0.6378322417003632</v>
       </c>
       <c r="G136" t="n">
-        <v>0.9935631616607268</v>
+        <v>1.110673194632721</v>
       </c>
       <c r="H136" t="n">
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>20.36502471853512</v>
+        <v>20.32149686907976</v>
       </c>
       <c r="J136" t="n">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="K136" t="n">
         <v>1</v>
@@ -5893,7 +5893,7 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>Sim234</t>
+          <t>Sim356</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5909,19 +5909,19 @@
         <v>0.5</v>
       </c>
       <c r="F137" t="n">
-        <v>0.5</v>
+        <v>0.5294250520646335</v>
       </c>
       <c r="G137" t="n">
-        <v>1.02234780905201</v>
+        <v>0.9426532296751616</v>
       </c>
       <c r="H137" t="n">
-        <v>0.5459993800735286</v>
+        <v>0.5</v>
       </c>
       <c r="I137" t="n">
-        <v>20.37351953762214</v>
+        <v>20.32274622971358</v>
       </c>
       <c r="J137" t="n">
-        <v>234</v>
+        <v>356</v>
       </c>
       <c r="K137" t="n">
         <v>1</v>
@@ -5933,7 +5933,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>Sim237</t>
+          <t>Sim245</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5949,19 +5949,19 @@
         <v>0.5</v>
       </c>
       <c r="F138" t="n">
-        <v>0.5</v>
+        <v>0.7933642490447225</v>
       </c>
       <c r="G138" t="n">
-        <v>0.7836441010248021</v>
+        <v>0.6655950221897429</v>
       </c>
       <c r="H138" t="n">
-        <v>0.5584045513076104</v>
+        <v>0.5</v>
       </c>
       <c r="I138" t="n">
-        <v>20.37393649234316</v>
+        <v>20.35196358649909</v>
       </c>
       <c r="J138" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="K138" t="n">
         <v>1</v>
@@ -5973,7 +5973,7 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>Sim309</t>
+          <t>Sim285</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5989,19 +5989,19 @@
         <v>0.5</v>
       </c>
       <c r="F139" t="n">
-        <v>0.5190894428560261</v>
+        <v>0.7933996952180886</v>
       </c>
       <c r="G139" t="n">
-        <v>0.9630537106007148</v>
+        <v>1.088849658652794</v>
       </c>
       <c r="H139" t="n">
-        <v>0.5</v>
+        <v>0.6351747750136939</v>
       </c>
       <c r="I139" t="n">
-        <v>20.37485884286609</v>
+        <v>20.35727000704251</v>
       </c>
       <c r="J139" t="n">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="K139" t="n">
         <v>1</v>
@@ -6013,7 +6013,7 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>Sim280</t>
+          <t>Sim313</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -6029,19 +6029,19 @@
         <v>0.5</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7091296384427456</v>
+        <v>0.5537108322845353</v>
       </c>
       <c r="G140" t="n">
-        <v>0.6384470466965465</v>
+        <v>0.9935631616607268</v>
       </c>
       <c r="H140" t="n">
         <v>0.5</v>
       </c>
       <c r="I140" t="n">
-        <v>20.38387565619671</v>
+        <v>20.36502471853512</v>
       </c>
       <c r="J140" t="n">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="K140" t="n">
         <v>1</v>
@@ -6053,7 +6053,7 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>Sim270</t>
+          <t>Sim234</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -6072,16 +6072,16 @@
         <v>0.5</v>
       </c>
       <c r="G141" t="n">
-        <v>0.9240779891219733</v>
+        <v>1.02234780905201</v>
       </c>
       <c r="H141" t="n">
-        <v>0.5</v>
+        <v>0.5459993800735286</v>
       </c>
       <c r="I141" t="n">
-        <v>20.38393873145821</v>
+        <v>20.37351953762214</v>
       </c>
       <c r="J141" t="n">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="K141" t="n">
         <v>1</v>
@@ -6093,7 +6093,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>Sim348</t>
+          <t>Sim237</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -6109,19 +6109,19 @@
         <v>0.5</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5522681579768032</v>
+        <v>0.5</v>
       </c>
       <c r="G142" t="n">
-        <v>1.022056526144993</v>
+        <v>0.7836441010248021</v>
       </c>
       <c r="H142" t="n">
-        <v>0.5111441898698422</v>
+        <v>0.5584045513076104</v>
       </c>
       <c r="I142" t="n">
-        <v>20.38804080082519</v>
+        <v>20.37393649234316</v>
       </c>
       <c r="J142" t="n">
-        <v>348</v>
+        <v>237</v>
       </c>
       <c r="K142" t="n">
         <v>1</v>
@@ -6133,7 +6133,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>Sim292</t>
+          <t>Sim309</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -6149,19 +6149,19 @@
         <v>0.5</v>
       </c>
       <c r="F143" t="n">
-        <v>0.5328145212757545</v>
+        <v>0.5190894428560261</v>
       </c>
       <c r="G143" t="n">
-        <v>1.076609601860213</v>
+        <v>0.9630537106007148</v>
       </c>
       <c r="H143" t="n">
-        <v>0.5823108401642222</v>
+        <v>0.5</v>
       </c>
       <c r="I143" t="n">
-        <v>20.38991522062162</v>
+        <v>20.37485884286609</v>
       </c>
       <c r="J143" t="n">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="K143" t="n">
         <v>1</v>
@@ -6173,7 +6173,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>Sim244</t>
+          <t>Sim256</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -6192,16 +6192,16 @@
         <v>0.5</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9656131227983664</v>
+        <v>0.8784465181136041</v>
       </c>
       <c r="H144" t="n">
-        <v>0.5047845544304523</v>
+        <v>0.7378118011167875</v>
       </c>
       <c r="I144" t="n">
-        <v>20.39243364354064</v>
+        <v>20.37584345528036</v>
       </c>
       <c r="J144" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="K144" t="n">
         <v>1</v>
@@ -6213,7 +6213,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>Sim277</t>
+          <t>Sim280</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -6226,22 +6226,22 @@
         <v>0.5</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5147784239166863</v>
+        <v>0.5</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5</v>
+        <v>0.7091296384427456</v>
       </c>
       <c r="G145" t="n">
-        <v>0.752407321762452</v>
+        <v>0.6384470466965465</v>
       </c>
       <c r="H145" t="n">
-        <v>0.5750980196230534</v>
+        <v>0.5</v>
       </c>
       <c r="I145" t="n">
-        <v>20.41849560077103</v>
+        <v>20.38387565619671</v>
       </c>
       <c r="J145" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K145" t="n">
         <v>1</v>
@@ -6253,7 +6253,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>Sim308</t>
+          <t>Sim270</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -6269,19 +6269,19 @@
         <v>0.5</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5867992945513181</v>
+        <v>0.5</v>
       </c>
       <c r="G146" t="n">
-        <v>1.080220096804596</v>
+        <v>0.9240779891219733</v>
       </c>
       <c r="H146" t="n">
         <v>0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>20.42319990605844</v>
+        <v>20.38393873145821</v>
       </c>
       <c r="J146" t="n">
-        <v>308</v>
+        <v>270</v>
       </c>
       <c r="K146" t="n">
         <v>1</v>
@@ -6293,7 +6293,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>Sim319</t>
+          <t>Sim348</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -6309,19 +6309,19 @@
         <v>0.5</v>
       </c>
       <c r="F147" t="n">
-        <v>0.594866226446023</v>
+        <v>0.5522681579768032</v>
       </c>
       <c r="G147" t="n">
-        <v>0.7056929917391355</v>
+        <v>1.022056526144993</v>
       </c>
       <c r="H147" t="n">
-        <v>0.5</v>
+        <v>0.5111441898698422</v>
       </c>
       <c r="I147" t="n">
-        <v>20.43147458710848</v>
+        <v>20.38804080082519</v>
       </c>
       <c r="J147" t="n">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="K147" t="n">
         <v>1</v>
@@ -6333,7 +6333,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>Sim318</t>
+          <t>Sim292</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -6349,19 +6349,19 @@
         <v>0.5</v>
       </c>
       <c r="F148" t="n">
-        <v>0.7383605247207128</v>
+        <v>0.5328145212757545</v>
       </c>
       <c r="G148" t="n">
-        <v>1.11794119435376</v>
+        <v>1.076609601860213</v>
       </c>
       <c r="H148" t="n">
-        <v>0.624282182781108</v>
+        <v>0.5823108401642222</v>
       </c>
       <c r="I148" t="n">
-        <v>20.44256787131703</v>
+        <v>20.38991522062162</v>
       </c>
       <c r="J148" t="n">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="K148" t="n">
         <v>1</v>
@@ -6373,7 +6373,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>Sim272</t>
+          <t>Sim244</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -6392,16 +6392,16 @@
         <v>0.5</v>
       </c>
       <c r="G149" t="n">
-        <v>0.9819468425194768</v>
+        <v>0.9656131227983664</v>
       </c>
       <c r="H149" t="n">
-        <v>0.5</v>
+        <v>0.5047845544304523</v>
       </c>
       <c r="I149" t="n">
-        <v>20.44515119871707</v>
+        <v>20.39243364354064</v>
       </c>
       <c r="J149" t="n">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="K149" t="n">
         <v>1</v>
@@ -6413,7 +6413,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>Sim247</t>
+          <t>Sim277</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -6426,22 +6426,22 @@
         <v>0.5</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5</v>
+        <v>0.5147784239166863</v>
       </c>
       <c r="F150" t="n">
         <v>0.5</v>
       </c>
       <c r="G150" t="n">
-        <v>0.8025758023984899</v>
+        <v>0.752407321762452</v>
       </c>
       <c r="H150" t="n">
-        <v>0.5</v>
+        <v>0.5750980196230534</v>
       </c>
       <c r="I150" t="n">
-        <v>20.44535016680722</v>
+        <v>20.41849560077103</v>
       </c>
       <c r="J150" t="n">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="K150" t="n">
         <v>1</v>
@@ -6453,7 +6453,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>Sim351</t>
+          <t>Sim308</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -6469,19 +6469,19 @@
         <v>0.5</v>
       </c>
       <c r="F151" t="n">
-        <v>0.5710376948058525</v>
+        <v>0.5867992945513181</v>
       </c>
       <c r="G151" t="n">
-        <v>1.074381284459689</v>
+        <v>1.080220096804596</v>
       </c>
       <c r="H151" t="n">
         <v>0.5</v>
       </c>
       <c r="I151" t="n">
-        <v>20.45484898909448</v>
+        <v>20.42319990605844</v>
       </c>
       <c r="J151" t="n">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="K151" t="n">
         <v>1</v>
@@ -6493,7 +6493,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>Sim379</t>
+          <t>Sim319</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -6509,19 +6509,19 @@
         <v>0.5</v>
       </c>
       <c r="F152" t="n">
-        <v>0.6795426354162071</v>
+        <v>0.594866226446023</v>
       </c>
       <c r="G152" t="n">
-        <v>1.162257024044162</v>
+        <v>0.7056929917391355</v>
       </c>
       <c r="H152" t="n">
         <v>0.5</v>
       </c>
       <c r="I152" t="n">
-        <v>20.45720263532579</v>
+        <v>20.43147458710848</v>
       </c>
       <c r="J152" t="n">
-        <v>379</v>
+        <v>319</v>
       </c>
       <c r="K152" t="n">
         <v>1</v>
@@ -6533,7 +6533,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>Sim289</t>
+          <t>Sim318</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -6549,19 +6549,19 @@
         <v>0.5</v>
       </c>
       <c r="F153" t="n">
-        <v>0.771809963708055</v>
+        <v>0.7383605247207128</v>
       </c>
       <c r="G153" t="n">
-        <v>0.6380831428980812</v>
+        <v>1.11794119435376</v>
       </c>
       <c r="H153" t="n">
-        <v>0.5</v>
+        <v>0.624282182781108</v>
       </c>
       <c r="I153" t="n">
-        <v>20.46647646440622</v>
+        <v>20.44256787131703</v>
       </c>
       <c r="J153" t="n">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="K153" t="n">
         <v>1</v>
@@ -6573,7 +6573,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>Sim281</t>
+          <t>Sim272</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -6592,16 +6592,16 @@
         <v>0.5</v>
       </c>
       <c r="G154" t="n">
-        <v>1.082185454943174</v>
+        <v>0.9819468425194768</v>
       </c>
       <c r="H154" t="n">
-        <v>0.582253421373274</v>
+        <v>0.5</v>
       </c>
       <c r="I154" t="n">
-        <v>20.50854643598103</v>
+        <v>20.44515119871707</v>
       </c>
       <c r="J154" t="n">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="K154" t="n">
         <v>1</v>
@@ -6613,7 +6613,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>Sim321</t>
+          <t>Sim247</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -6629,19 +6629,19 @@
         <v>0.5</v>
       </c>
       <c r="F155" t="n">
-        <v>0.5077256681205352</v>
+        <v>0.5</v>
       </c>
       <c r="G155" t="n">
-        <v>0.7694545256294196</v>
+        <v>0.8025758023984899</v>
       </c>
       <c r="H155" t="n">
         <v>0.5</v>
       </c>
       <c r="I155" t="n">
-        <v>20.52737166712355</v>
+        <v>20.44535016680722</v>
       </c>
       <c r="J155" t="n">
-        <v>321</v>
+        <v>247</v>
       </c>
       <c r="K155" t="n">
         <v>1</v>
@@ -6653,7 +6653,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>Sim258</t>
+          <t>Sim351</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -6669,19 +6669,19 @@
         <v>0.5</v>
       </c>
       <c r="F156" t="n">
-        <v>0.5</v>
+        <v>0.5710376948058525</v>
       </c>
       <c r="G156" t="n">
-        <v>0.7226494366180606</v>
+        <v>1.074381284459689</v>
       </c>
       <c r="H156" t="n">
-        <v>0.5540399568954212</v>
+        <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>20.53365825207632</v>
+        <v>20.45484898909448</v>
       </c>
       <c r="J156" t="n">
-        <v>258</v>
+        <v>351</v>
       </c>
       <c r="K156" t="n">
         <v>1</v>
@@ -6693,7 +6693,7 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>Sim274</t>
+          <t>Sim379</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -6709,19 +6709,19 @@
         <v>0.5</v>
       </c>
       <c r="F157" t="n">
-        <v>0.5</v>
+        <v>0.6795426354162071</v>
       </c>
       <c r="G157" t="n">
-        <v>0.7338926966426559</v>
+        <v>1.162257024044162</v>
       </c>
       <c r="H157" t="n">
-        <v>0.5434253264349942</v>
+        <v>0.5</v>
       </c>
       <c r="I157" t="n">
-        <v>20.53634797967757</v>
+        <v>20.45720263532579</v>
       </c>
       <c r="J157" t="n">
-        <v>274</v>
+        <v>379</v>
       </c>
       <c r="K157" t="n">
         <v>1</v>
@@ -6733,7 +6733,7 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>Sim382</t>
+          <t>Sim289</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -6749,19 +6749,19 @@
         <v>0.5</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7153750688378767</v>
+        <v>0.771809963708055</v>
       </c>
       <c r="G158" t="n">
-        <v>1.16752062381661</v>
+        <v>0.6380831428980812</v>
       </c>
       <c r="H158" t="n">
-        <v>0.59142055947406</v>
+        <v>0.5</v>
       </c>
       <c r="I158" t="n">
-        <v>20.53742891152775</v>
+        <v>20.46647646440622</v>
       </c>
       <c r="J158" t="n">
-        <v>382</v>
+        <v>289</v>
       </c>
       <c r="K158" t="n">
         <v>1</v>
@@ -6773,7 +6773,7 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>Sim320</t>
+          <t>Sim281</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -6789,19 +6789,19 @@
         <v>0.5</v>
       </c>
       <c r="F159" t="n">
-        <v>0.7398522493142102</v>
+        <v>0.5</v>
       </c>
       <c r="G159" t="n">
-        <v>1.153227426111164</v>
+        <v>1.082185454943174</v>
       </c>
       <c r="H159" t="n">
-        <v>0.5</v>
+        <v>0.582253421373274</v>
       </c>
       <c r="I159" t="n">
-        <v>20.56030541587842</v>
+        <v>20.50854643598103</v>
       </c>
       <c r="J159" t="n">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="K159" t="n">
         <v>1</v>
@@ -6813,7 +6813,7 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>Sim317</t>
+          <t>Sim321</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -6829,19 +6829,19 @@
         <v>0.5</v>
       </c>
       <c r="F160" t="n">
-        <v>0.5447688426067595</v>
+        <v>0.5077256681205352</v>
       </c>
       <c r="G160" t="n">
-        <v>0.7203749170207915</v>
+        <v>0.7694545256294196</v>
       </c>
       <c r="H160" t="n">
         <v>0.5</v>
       </c>
       <c r="I160" t="n">
-        <v>20.56146182985639</v>
+        <v>20.52737166712355</v>
       </c>
       <c r="J160" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K160" t="n">
         <v>1</v>
@@ -6853,7 +6853,7 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>Sim304</t>
+          <t>Sim258</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -6869,19 +6869,19 @@
         <v>0.5</v>
       </c>
       <c r="F161" t="n">
-        <v>0.538687131025024</v>
+        <v>0.5</v>
       </c>
       <c r="G161" t="n">
-        <v>1.083044118563511</v>
+        <v>0.7226494366180606</v>
       </c>
       <c r="H161" t="n">
-        <v>0.5</v>
+        <v>0.5540399568954212</v>
       </c>
       <c r="I161" t="n">
-        <v>20.5736899442347</v>
+        <v>20.53365825207632</v>
       </c>
       <c r="J161" t="n">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="K161" t="n">
         <v>1</v>
@@ -6893,7 +6893,7 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>Sim344</t>
+          <t>Sim274</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -6909,19 +6909,19 @@
         <v>0.5</v>
       </c>
       <c r="F162" t="n">
-        <v>0.5966034710232989</v>
+        <v>0.5</v>
       </c>
       <c r="G162" t="n">
-        <v>1.12452832336882</v>
+        <v>0.7338926966426559</v>
       </c>
       <c r="H162" t="n">
-        <v>0.5</v>
+        <v>0.5434253264349942</v>
       </c>
       <c r="I162" t="n">
-        <v>20.58196155499765</v>
+        <v>20.53634797967757</v>
       </c>
       <c r="J162" t="n">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="K162" t="n">
         <v>1</v>
@@ -6933,7 +6933,7 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>Sim290</t>
+          <t>Sim382</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -6949,19 +6949,19 @@
         <v>0.5</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5740808760877313</v>
+        <v>0.7153750688378767</v>
       </c>
       <c r="G163" t="n">
-        <v>0.6668480017443186</v>
+        <v>1.16752062381661</v>
       </c>
       <c r="H163" t="n">
-        <v>0.5069160061447572</v>
+        <v>0.59142055947406</v>
       </c>
       <c r="I163" t="n">
-        <v>20.58856141652855</v>
+        <v>20.53742891152775</v>
       </c>
       <c r="J163" t="n">
-        <v>290</v>
+        <v>382</v>
       </c>
       <c r="K163" t="n">
         <v>1</v>
@@ -6973,7 +6973,7 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>Sim307</t>
+          <t>Sim320</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -6989,19 +6989,19 @@
         <v>0.5</v>
       </c>
       <c r="F164" t="n">
-        <v>0.5034014714762135</v>
+        <v>0.7398522493142102</v>
       </c>
       <c r="G164" t="n">
-        <v>1.064580645275084</v>
+        <v>1.153227426111164</v>
       </c>
       <c r="H164" t="n">
         <v>0.5</v>
       </c>
       <c r="I164" t="n">
-        <v>20.5964417670618</v>
+        <v>20.56030541587842</v>
       </c>
       <c r="J164" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="K164" t="n">
         <v>1</v>
@@ -7013,7 +7013,7 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>Sim353</t>
+          <t>Sim317</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -7029,19 +7029,19 @@
         <v>0.5</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7243676306564599</v>
+        <v>0.5447688426067595</v>
       </c>
       <c r="G165" t="n">
-        <v>1.163954212246951</v>
+        <v>0.7203749170207915</v>
       </c>
       <c r="H165" t="n">
-        <v>0.5030877041989684</v>
+        <v>0.5</v>
       </c>
       <c r="I165" t="n">
-        <v>20.60358078388036</v>
+        <v>20.56146182985639</v>
       </c>
       <c r="J165" t="n">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="K165" t="n">
         <v>1</v>
@@ -7053,7 +7053,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>Sim364</t>
+          <t>Sim304</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -7069,19 +7069,19 @@
         <v>0.5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.5976530619711389</v>
+        <v>0.538687131025024</v>
       </c>
       <c r="G166" t="n">
-        <v>1.133595941959186</v>
+        <v>1.083044118563511</v>
       </c>
       <c r="H166" t="n">
         <v>0.5</v>
       </c>
       <c r="I166" t="n">
-        <v>20.6162601095504</v>
+        <v>20.5736899442347</v>
       </c>
       <c r="J166" t="n">
-        <v>364</v>
+        <v>304</v>
       </c>
       <c r="K166" t="n">
         <v>1</v>
@@ -7093,7 +7093,7 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>Sim357</t>
+          <t>Sim344</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -7109,19 +7109,19 @@
         <v>0.5</v>
       </c>
       <c r="F167" t="n">
-        <v>0.5</v>
+        <v>0.5966034710232989</v>
       </c>
       <c r="G167" t="n">
-        <v>1.07590414010898</v>
+        <v>1.12452832336882</v>
       </c>
       <c r="H167" t="n">
         <v>0.5</v>
       </c>
       <c r="I167" t="n">
-        <v>20.62999838683118</v>
+        <v>20.58196155499765</v>
       </c>
       <c r="J167" t="n">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="K167" t="n">
         <v>1</v>
@@ -7133,7 +7133,7 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>Sim282</t>
+          <t>Sim290</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -7149,19 +7149,19 @@
         <v>0.5</v>
       </c>
       <c r="F168" t="n">
-        <v>0.5</v>
+        <v>0.5740808760877313</v>
       </c>
       <c r="G168" t="n">
-        <v>0.7246741189215633</v>
+        <v>0.6668480017443186</v>
       </c>
       <c r="H168" t="n">
-        <v>0.5</v>
+        <v>0.5069160061447572</v>
       </c>
       <c r="I168" t="n">
-        <v>20.64189596551023</v>
+        <v>20.58856141652855</v>
       </c>
       <c r="J168" t="n">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="K168" t="n">
         <v>1</v>
@@ -7173,7 +7173,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>Sim316</t>
+          <t>Sim307</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -7189,19 +7189,19 @@
         <v>0.5</v>
       </c>
       <c r="F169" t="n">
-        <v>0.5599291462328998</v>
+        <v>0.5034014714762135</v>
       </c>
       <c r="G169" t="n">
-        <v>1.133171404446818</v>
+        <v>1.064580645275084</v>
       </c>
       <c r="H169" t="n">
-        <v>0.521038499785076</v>
+        <v>0.5</v>
       </c>
       <c r="I169" t="n">
-        <v>20.68740023927995</v>
+        <v>20.5964417670618</v>
       </c>
       <c r="J169" t="n">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="K169" t="n">
         <v>1</v>
@@ -7213,7 +7213,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>Sim223</t>
+          <t>Sim353</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -7229,19 +7229,19 @@
         <v>0.5</v>
       </c>
       <c r="F170" t="n">
-        <v>0.6067255853582709</v>
+        <v>0.7243676306564599</v>
       </c>
       <c r="G170" t="n">
-        <v>0.6207784286790614</v>
+        <v>1.163954212246951</v>
       </c>
       <c r="H170" t="n">
-        <v>0.5342541582165832</v>
+        <v>0.5030877041989684</v>
       </c>
       <c r="I170" t="n">
-        <v>20.69833427424454</v>
+        <v>20.60358078388036</v>
       </c>
       <c r="J170" t="n">
-        <v>223</v>
+        <v>353</v>
       </c>
       <c r="K170" t="n">
         <v>1</v>
@@ -7253,7 +7253,7 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>Sim271</t>
+          <t>Sim364</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -7269,19 +7269,19 @@
         <v>0.5</v>
       </c>
       <c r="F171" t="n">
-        <v>0.5</v>
+        <v>0.5976530619711389</v>
       </c>
       <c r="G171" t="n">
-        <v>1.108076206228105</v>
+        <v>1.133595941959186</v>
       </c>
       <c r="H171" t="n">
-        <v>0.530274091487096</v>
+        <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>20.70300386109648</v>
+        <v>20.6162601095504</v>
       </c>
       <c r="J171" t="n">
-        <v>271</v>
+        <v>364</v>
       </c>
       <c r="K171" t="n">
         <v>1</v>
@@ -7293,7 +7293,7 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>Sim216</t>
+          <t>Sim357</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -7309,19 +7309,19 @@
         <v>0.5</v>
       </c>
       <c r="F172" t="n">
-        <v>0.6760692817448919</v>
+        <v>0.5</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5266170563953649</v>
+        <v>1.07590414010898</v>
       </c>
       <c r="H172" t="n">
-        <v>0.5048937497703346</v>
+        <v>0.5</v>
       </c>
       <c r="I172" t="n">
-        <v>20.79640121217077</v>
+        <v>20.62999838683118</v>
       </c>
       <c r="J172" t="n">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="K172" t="n">
         <v>1</v>
@@ -7333,7 +7333,7 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>Sim329</t>
+          <t>Sim282</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -7349,19 +7349,19 @@
         <v>0.5</v>
       </c>
       <c r="F173" t="n">
-        <v>0.5128908918951433</v>
+        <v>0.5</v>
       </c>
       <c r="G173" t="n">
-        <v>1.128946183596914</v>
+        <v>0.7246741189215633</v>
       </c>
       <c r="H173" t="n">
         <v>0.5</v>
       </c>
       <c r="I173" t="n">
-        <v>20.85962980454831</v>
+        <v>20.64189596551023</v>
       </c>
       <c r="J173" t="n">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="K173" t="n">
         <v>1</v>
@@ -7373,7 +7373,7 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>Sim347</t>
+          <t>Sim316</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -7389,19 +7389,19 @@
         <v>0.5</v>
       </c>
       <c r="F174" t="n">
-        <v>0.6700772507072326</v>
+        <v>0.5599291462328998</v>
       </c>
       <c r="G174" t="n">
-        <v>1.22237818013326</v>
+        <v>1.133171404446818</v>
       </c>
       <c r="H174" t="n">
-        <v>0.6122791294519812</v>
+        <v>0.521038499785076</v>
       </c>
       <c r="I174" t="n">
-        <v>20.89350971115989</v>
+        <v>20.68740023927995</v>
       </c>
       <c r="J174" t="n">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="K174" t="n">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>Sim269</t>
+          <t>Sim223</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -7429,19 +7429,19 @@
         <v>0.5</v>
       </c>
       <c r="F175" t="n">
-        <v>0.5</v>
+        <v>0.6067255853582709</v>
       </c>
       <c r="G175" t="n">
-        <v>1.13648550166604</v>
+        <v>0.6207784286790614</v>
       </c>
       <c r="H175" t="n">
-        <v>0.5</v>
+        <v>0.5342541582165832</v>
       </c>
       <c r="I175" t="n">
-        <v>20.89888109729352</v>
+        <v>20.69833427424454</v>
       </c>
       <c r="J175" t="n">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="K175" t="n">
         <v>1</v>
@@ -7453,7 +7453,7 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>Sim287</t>
+          <t>Sim271</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -7472,16 +7472,16 @@
         <v>0.5</v>
       </c>
       <c r="G176" t="n">
-        <v>1.141595309528267</v>
+        <v>1.108076206228105</v>
       </c>
       <c r="H176" t="n">
-        <v>0.5</v>
+        <v>0.530274091487096</v>
       </c>
       <c r="I176" t="n">
-        <v>20.9181916966424</v>
+        <v>20.70300386109648</v>
       </c>
       <c r="J176" t="n">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="K176" t="n">
         <v>1</v>
@@ -7493,7 +7493,7 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>Sim275</t>
+          <t>Sim216</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -7509,19 +7509,19 @@
         <v>0.5</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5068596678307389</v>
+        <v>0.6760692817448919</v>
       </c>
       <c r="G177" t="n">
-        <v>0.6346941229144386</v>
+        <v>0.5266170563953649</v>
       </c>
       <c r="H177" t="n">
-        <v>0.5</v>
+        <v>0.5048937497703346</v>
       </c>
       <c r="I177" t="n">
-        <v>20.93969743906414</v>
+        <v>20.79640121217077</v>
       </c>
       <c r="J177" t="n">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="K177" t="n">
         <v>1</v>
@@ -7533,7 +7533,7 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>Sim276</t>
+          <t>Sim329</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -7549,19 +7549,19 @@
         <v>0.5</v>
       </c>
       <c r="F178" t="n">
-        <v>0.5</v>
+        <v>0.5128908918951433</v>
       </c>
       <c r="G178" t="n">
-        <v>0.6243084557498045</v>
+        <v>1.128946183596914</v>
       </c>
       <c r="H178" t="n">
-        <v>0.6100553669963437</v>
+        <v>0.5</v>
       </c>
       <c r="I178" t="n">
-        <v>20.94601932117697</v>
+        <v>20.85962980454831</v>
       </c>
       <c r="J178" t="n">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="K178" t="n">
         <v>1</v>
@@ -7573,7 +7573,7 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>Sim322</t>
+          <t>Sim347</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -7589,19 +7589,19 @@
         <v>0.5</v>
       </c>
       <c r="F179" t="n">
-        <v>0.5</v>
+        <v>0.6700772507072326</v>
       </c>
       <c r="G179" t="n">
-        <v>1.155123107068126</v>
+        <v>1.22237818013326</v>
       </c>
       <c r="H179" t="n">
-        <v>0.5</v>
+        <v>0.6122791294519812</v>
       </c>
       <c r="I179" t="n">
-        <v>20.96254348975413</v>
+        <v>20.89350971115989</v>
       </c>
       <c r="J179" t="n">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="K179" t="n">
         <v>1</v>
@@ -7613,7 +7613,7 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>Sim330</t>
+          <t>Sim269</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -7632,16 +7632,16 @@
         <v>0.5</v>
       </c>
       <c r="G180" t="n">
-        <v>1.162020244941212</v>
+        <v>1.13648550166604</v>
       </c>
       <c r="H180" t="n">
         <v>0.5</v>
       </c>
       <c r="I180" t="n">
-        <v>20.98897974185669</v>
+        <v>20.89888109729352</v>
       </c>
       <c r="J180" t="n">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c r="K180" t="n">
         <v>1</v>
@@ -7653,7 +7653,7 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>Sim159</t>
+          <t>Sim287</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -7669,19 +7669,19 @@
         <v>0.5</v>
       </c>
       <c r="F181" t="n">
-        <v>0.6932884675905744</v>
+        <v>0.5</v>
       </c>
       <c r="G181" t="n">
-        <v>1.190021281267333</v>
+        <v>1.141595309528267</v>
       </c>
       <c r="H181" t="n">
-        <v>0.7095939265952046</v>
+        <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>21.00872264335718</v>
+        <v>20.9181916966424</v>
       </c>
       <c r="J181" t="n">
-        <v>159</v>
+        <v>287</v>
       </c>
       <c r="K181" t="n">
         <v>1</v>
@@ -7693,35 +7693,35 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>Sim337</t>
+          <t>Sim275</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>0.5</v>
       </c>
       <c r="C182" t="n">
-        <v>0.5078667772133887</v>
+        <v>0.5</v>
       </c>
       <c r="D182" t="n">
-        <v>0.5132437757884762</v>
+        <v>0.5</v>
       </c>
       <c r="E182" t="n">
         <v>0.5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.7244418124092183</v>
+        <v>0.5068596678307389</v>
       </c>
       <c r="G182" t="n">
-        <v>1.224446797917898</v>
+        <v>0.6346941229144386</v>
       </c>
       <c r="H182" t="n">
         <v>0.5</v>
       </c>
       <c r="I182" t="n">
-        <v>21.00930071573778</v>
+        <v>20.93969743906414</v>
       </c>
       <c r="J182" t="n">
-        <v>337</v>
+        <v>275</v>
       </c>
       <c r="K182" t="n">
         <v>1</v>
@@ -7733,7 +7733,7 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>Sim365</t>
+          <t>Sim276</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -7749,19 +7749,19 @@
         <v>0.5</v>
       </c>
       <c r="F183" t="n">
-        <v>0.5253870154473178</v>
+        <v>0.5</v>
       </c>
       <c r="G183" t="n">
-        <v>1.191231424314191</v>
+        <v>0.6243084557498045</v>
       </c>
       <c r="H183" t="n">
-        <v>0.5</v>
+        <v>0.6100553669963437</v>
       </c>
       <c r="I183" t="n">
-        <v>21.09113883297131</v>
+        <v>20.94601932117697</v>
       </c>
       <c r="J183" t="n">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="K183" t="n">
         <v>1</v>
@@ -7773,7 +7773,7 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>Sim306</t>
+          <t>Sim322</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -7792,16 +7792,16 @@
         <v>0.5</v>
       </c>
       <c r="G184" t="n">
-        <v>1.200159002068001</v>
+        <v>1.155123107068126</v>
       </c>
       <c r="H184" t="n">
-        <v>0.5364623197354561</v>
+        <v>0.5</v>
       </c>
       <c r="I184" t="n">
-        <v>21.09672635180324</v>
+        <v>20.96254348975413</v>
       </c>
       <c r="J184" t="n">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="K184" t="n">
         <v>1</v>
@@ -7813,7 +7813,7 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>Sim372</t>
+          <t>Sim330</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -7823,25 +7823,25 @@
         <v>0.5</v>
       </c>
       <c r="D185" t="n">
-        <v>0.5074155295315639</v>
+        <v>0.5</v>
       </c>
       <c r="E185" t="n">
         <v>0.5</v>
       </c>
       <c r="F185" t="n">
-        <v>0.7347170704169769</v>
+        <v>0.5</v>
       </c>
       <c r="G185" t="n">
-        <v>1.286981484418346</v>
+        <v>1.162020244941212</v>
       </c>
       <c r="H185" t="n">
         <v>0.5</v>
       </c>
       <c r="I185" t="n">
-        <v>21.30145281107432</v>
+        <v>20.98897974185669</v>
       </c>
       <c r="J185" t="n">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="K185" t="n">
         <v>1</v>
@@ -7853,7 +7853,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>Sim284</t>
+          <t>Sim159</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -7869,19 +7869,19 @@
         <v>0.5</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5</v>
+        <v>0.6932884675905744</v>
       </c>
       <c r="G186" t="n">
-        <v>0.5306848739559596</v>
+        <v>1.190021281267333</v>
       </c>
       <c r="H186" t="n">
-        <v>0.5</v>
+        <v>0.7095939265952046</v>
       </c>
       <c r="I186" t="n">
-        <v>21.31267491884154</v>
+        <v>21.00872264335718</v>
       </c>
       <c r="J186" t="n">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="K186" t="n">
         <v>1</v>
@@ -7893,127 +7893,127 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>Sim163</t>
+          <t>Sim337</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.5548301043338719</v>
+        <v>0.5</v>
       </c>
       <c r="C187" t="n">
-        <v>0.6530043816037546</v>
+        <v>0.5078667772133887</v>
       </c>
       <c r="D187" t="n">
-        <v>0.5</v>
+        <v>0.5132437757884762</v>
       </c>
       <c r="E187" t="n">
         <v>0.5</v>
       </c>
       <c r="F187" t="n">
-        <v>0.6846797134414886</v>
+        <v>0.7244418124092183</v>
       </c>
       <c r="G187" t="n">
-        <v>0.90828851800668</v>
+        <v>1.224446797917898</v>
       </c>
       <c r="H187" t="n">
-        <v>0.5229273799803165</v>
+        <v>0.5</v>
       </c>
       <c r="I187" t="n">
-        <v>20.93334341816082</v>
+        <v>21.00930071573778</v>
       </c>
       <c r="J187" t="n">
-        <v>163</v>
+        <v>337</v>
       </c>
       <c r="K187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L187" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>Sim302</t>
+          <t>Sim365</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>0.5</v>
       </c>
       <c r="C188" t="n">
-        <v>0.5373059077062148</v>
+        <v>0.5</v>
       </c>
       <c r="D188" t="n">
-        <v>0.5430253616547421</v>
+        <v>0.5</v>
       </c>
       <c r="E188" t="n">
         <v>0.5</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6788397443319993</v>
+        <v>0.5253870154473178</v>
       </c>
       <c r="G188" t="n">
-        <v>1.05083185310128</v>
+        <v>1.191231424314191</v>
       </c>
       <c r="H188" t="n">
         <v>0.5</v>
       </c>
       <c r="I188" t="n">
-        <v>20.36641708950523</v>
+        <v>21.09113883297131</v>
       </c>
       <c r="J188" t="n">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L188" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>Sim267</t>
+          <t>Sim306</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.5122925938903418</v>
+        <v>0.5</v>
       </c>
       <c r="C189" t="n">
-        <v>0.5620455600263251</v>
+        <v>0.5</v>
       </c>
       <c r="D189" t="n">
-        <v>0.5657181089379445</v>
+        <v>0.5</v>
       </c>
       <c r="E189" t="n">
         <v>0.5</v>
       </c>
       <c r="F189" t="n">
-        <v>0.6886759104133188</v>
+        <v>0.5</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7678830317156242</v>
+        <v>1.200159002068001</v>
       </c>
       <c r="H189" t="n">
-        <v>0.5</v>
+        <v>0.5364623197354561</v>
       </c>
       <c r="I189" t="n">
-        <v>20.57517918585355</v>
+        <v>21.09672635180324</v>
       </c>
       <c r="J189" t="n">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="K189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>Sim158</t>
+          <t>Sim372</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -8023,37 +8023,37 @@
         <v>0.5</v>
       </c>
       <c r="D190" t="n">
-        <v>0.5</v>
+        <v>0.5074155295315639</v>
       </c>
       <c r="E190" t="n">
-        <v>0.6148546382980264</v>
+        <v>0.5</v>
       </c>
       <c r="F190" t="n">
-        <v>0.7210108900395958</v>
+        <v>0.7347170704169769</v>
       </c>
       <c r="G190" t="n">
-        <v>0.834443993337176</v>
+        <v>1.286981484418346</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7332350698650159</v>
+        <v>0.5</v>
       </c>
       <c r="I190" t="n">
-        <v>20.79356906554032</v>
+        <v>21.30145281107432</v>
       </c>
       <c r="J190" t="n">
-        <v>158</v>
+        <v>372</v>
       </c>
       <c r="K190" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>Sim193</t>
+          <t>Sim284</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -8066,148 +8066,148 @@
         <v>0.5</v>
       </c>
       <c r="E191" t="n">
-        <v>0.5984129934950575</v>
+        <v>0.5</v>
       </c>
       <c r="F191" t="n">
-        <v>0.9434224443822048</v>
+        <v>0.5</v>
       </c>
       <c r="G191" t="n">
-        <v>0.8151071541476985</v>
+        <v>0.5306848739559596</v>
       </c>
       <c r="H191" t="n">
-        <v>0.6540371205408213</v>
+        <v>0.5</v>
       </c>
       <c r="I191" t="n">
-        <v>20.81724288797164</v>
+        <v>21.31267491884154</v>
       </c>
       <c r="J191" t="n">
-        <v>193</v>
+        <v>284</v>
       </c>
       <c r="K191" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>Sim230</t>
+          <t>Sim163</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.5</v>
+        <v>0.5548301043338719</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5</v>
+        <v>0.6530043816037546</v>
       </c>
       <c r="D192" t="n">
         <v>0.5</v>
       </c>
       <c r="E192" t="n">
-        <v>0.7175512954570658</v>
+        <v>0.5</v>
       </c>
       <c r="F192" t="n">
-        <v>0.7671425562522712</v>
+        <v>0.6846797134414886</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7709505675603744</v>
+        <v>0.90828851800668</v>
       </c>
       <c r="H192" t="n">
-        <v>0.6509088037508256</v>
+        <v>0.5229273799803165</v>
       </c>
       <c r="I192" t="n">
-        <v>21.00172427586616</v>
+        <v>20.93334341816082</v>
       </c>
       <c r="J192" t="n">
-        <v>230</v>
+        <v>163</v>
       </c>
       <c r="K192" t="n">
+        <v>2</v>
+      </c>
+      <c r="L192" t="n">
         <v>4</v>
-      </c>
-      <c r="L192" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>Sim219</t>
+          <t>Sim302</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>0.5</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5</v>
+        <v>0.5373059077062148</v>
       </c>
       <c r="D193" t="n">
-        <v>0.5</v>
+        <v>0.5430253616547421</v>
       </c>
       <c r="E193" t="n">
-        <v>0.6062286098624411</v>
+        <v>0.5</v>
       </c>
       <c r="F193" t="n">
-        <v>0.8488900333647152</v>
+        <v>0.6788397443319993</v>
       </c>
       <c r="G193" t="n">
-        <v>0.5489767765843757</v>
+        <v>1.05083185310128</v>
       </c>
       <c r="H193" t="n">
-        <v>0.6070288076127434</v>
+        <v>0.5</v>
       </c>
       <c r="I193" t="n">
-        <v>21.23326336133828</v>
+        <v>20.36641708950523</v>
       </c>
       <c r="J193" t="n">
-        <v>219</v>
+        <v>302</v>
       </c>
       <c r="K193" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>Sim156</t>
+          <t>Sim267</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.5</v>
+        <v>0.5122925938903418</v>
       </c>
       <c r="C194" t="n">
-        <v>0.5</v>
+        <v>0.5620455600263251</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5</v>
+        <v>0.5657181089379445</v>
       </c>
       <c r="E194" t="n">
-        <v>0.6083697637447741</v>
+        <v>0.5</v>
       </c>
       <c r="F194" t="n">
-        <v>1.109414974234838</v>
+        <v>0.6886759104133188</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7606435662030911</v>
+        <v>0.7678830317156242</v>
       </c>
       <c r="H194" t="n">
-        <v>0.7120782058261544</v>
+        <v>0.5</v>
       </c>
       <c r="I194" t="n">
-        <v>21.31861576498958</v>
+        <v>20.57517918585355</v>
       </c>
       <c r="J194" t="n">
-        <v>156</v>
+        <v>267</v>
       </c>
       <c r="K194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
